--- a/data/raw/TSM.xlsx
+++ b/data/raw/TSM.xlsx
@@ -468,5022 +468,5022 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45834</v>
+        <v>45845</v>
       </c>
       <c r="B2" t="n">
-        <v>221.5596618652344</v>
+        <v>226.6632385253906</v>
       </c>
       <c r="C2" t="n">
-        <v>222.7564329243529</v>
+        <v>230.0062714664003</v>
       </c>
       <c r="D2" t="n">
-        <v>220.2639937109393</v>
+        <v>224.9521662324545</v>
       </c>
       <c r="E2" t="n">
-        <v>222.5190527305437</v>
+        <v>229.0963366316631</v>
       </c>
       <c r="F2" t="n">
-        <v>7982200</v>
+        <v>13817500</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45835</v>
+        <v>45846</v>
       </c>
       <c r="B3" t="n">
-        <v>226.0698089599609</v>
+        <v>225.3675689697266</v>
       </c>
       <c r="C3" t="n">
-        <v>226.3764156301438</v>
+        <v>227.8105522444174</v>
       </c>
       <c r="D3" t="n">
-        <v>221.579461007304</v>
+        <v>225.0510620245914</v>
       </c>
       <c r="E3" t="n">
-        <v>221.8465118553492</v>
+        <v>227.2665653648924</v>
       </c>
       <c r="F3" t="n">
-        <v>13133000</v>
+        <v>8854400</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45838</v>
+        <v>45847</v>
       </c>
       <c r="B4" t="n">
-        <v>224.0125579833984</v>
+        <v>229.3040161132812</v>
       </c>
       <c r="C4" t="n">
-        <v>225.6543887018925</v>
+        <v>230.718381915776</v>
       </c>
       <c r="D4" t="n">
-        <v>222.3410415335963</v>
+        <v>227.7215267575379</v>
       </c>
       <c r="E4" t="n">
-        <v>224.9521634462919</v>
+        <v>227.9292212225116</v>
       </c>
       <c r="F4" t="n">
-        <v>9279800</v>
+        <v>9475300</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45839</v>
+        <v>45848</v>
       </c>
       <c r="B5" t="n">
-        <v>222.2223205566406</v>
+        <v>227.2467651367188</v>
       </c>
       <c r="C5" t="n">
-        <v>226.0994547426888</v>
+        <v>230.5007859278944</v>
       </c>
       <c r="D5" t="n">
-        <v>218.7606054627177</v>
+        <v>225.278542407666</v>
       </c>
       <c r="E5" t="n">
-        <v>224.9422395590086</v>
+        <v>230.2337350967803</v>
       </c>
       <c r="F5" t="n">
-        <v>9990200</v>
+        <v>13124700</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45840</v>
+        <v>45849</v>
       </c>
       <c r="B6" t="n">
-        <v>231.0447692871094</v>
+        <v>227.8797607421875</v>
       </c>
       <c r="C6" t="n">
-        <v>231.2623640214935</v>
+        <v>229.7293159867697</v>
       </c>
       <c r="D6" t="n">
-        <v>221.5497729797945</v>
+        <v>226.8906992544317</v>
       </c>
       <c r="E6" t="n">
-        <v>222.0245182675961</v>
+        <v>228.4732036715932</v>
       </c>
       <c r="F6" t="n">
-        <v>12012500</v>
+        <v>8817800</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45841</v>
+        <v>45852</v>
       </c>
       <c r="B7" t="n">
-        <v>232.2316589355469</v>
+        <v>226.168701171875</v>
       </c>
       <c r="C7" t="n">
-        <v>234.9812488842855</v>
+        <v>227.33580164011</v>
       </c>
       <c r="D7" t="n">
-        <v>230.7183959454815</v>
+        <v>223.8345153272864</v>
       </c>
       <c r="E7" t="n">
-        <v>231.3118238305155</v>
+        <v>226.8214854121481</v>
       </c>
       <c r="F7" t="n">
-        <v>7779600</v>
+        <v>10673500</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45845</v>
+        <v>45853</v>
       </c>
       <c r="B8" t="n">
-        <v>226.6632385253906</v>
+        <v>234.3581237792969</v>
       </c>
       <c r="C8" t="n">
-        <v>230.0062714664003</v>
+        <v>235.1098201921258</v>
       </c>
       <c r="D8" t="n">
-        <v>224.9521662324545</v>
+        <v>231.2920421272182</v>
       </c>
       <c r="E8" t="n">
-        <v>229.0963366316631</v>
+        <v>231.8953702571503</v>
       </c>
       <c r="F8" t="n">
-        <v>13817500</v>
+        <v>14270100</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45846</v>
+        <v>45854</v>
       </c>
       <c r="B9" t="n">
-        <v>225.3675689697266</v>
+        <v>234.9614410400391</v>
       </c>
       <c r="C9" t="n">
-        <v>227.8105522444174</v>
+        <v>235.7032371445645</v>
       </c>
       <c r="D9" t="n">
-        <v>225.0510620245914</v>
+        <v>231.5887377960789</v>
       </c>
       <c r="E9" t="n">
-        <v>227.2665653648924</v>
+        <v>233.8141261096551</v>
       </c>
       <c r="F9" t="n">
-        <v>8854400</v>
+        <v>15092800</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45847</v>
+        <v>45855</v>
       </c>
       <c r="B10" t="n">
-        <v>229.3040161132812</v>
+        <v>242.9135131835938</v>
       </c>
       <c r="C10" t="n">
-        <v>230.718381915776</v>
+        <v>245.5641907894646</v>
       </c>
       <c r="D10" t="n">
-        <v>227.7215267575379</v>
+        <v>238.7495575810806</v>
       </c>
       <c r="E10" t="n">
-        <v>227.9292212225116</v>
+        <v>243.1014221935387</v>
       </c>
       <c r="F10" t="n">
-        <v>9475300</v>
+        <v>27395700</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45848</v>
+        <v>45856</v>
       </c>
       <c r="B11" t="n">
-        <v>227.2467803955078</v>
+        <v>237.7703857421875</v>
       </c>
       <c r="C11" t="n">
-        <v>230.5008014051791</v>
+        <v>243.2794657076245</v>
       </c>
       <c r="D11" t="n">
-        <v>225.2785575342961</v>
+        <v>236.0790989775762</v>
       </c>
       <c r="E11" t="n">
-        <v>230.2337505561334</v>
+        <v>242.6266814758638</v>
       </c>
       <c r="F11" t="n">
-        <v>13124700</v>
+        <v>16252000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45849</v>
+        <v>45859</v>
       </c>
       <c r="B12" t="n">
-        <v>227.8797607421875</v>
+        <v>236.2373657226562</v>
       </c>
       <c r="C12" t="n">
-        <v>229.7293159867697</v>
+        <v>239.6891809970893</v>
       </c>
       <c r="D12" t="n">
-        <v>226.8906992544317</v>
+        <v>236.0988977043679</v>
       </c>
       <c r="E12" t="n">
-        <v>228.4732036715932</v>
+        <v>237.4934630700289</v>
       </c>
       <c r="F12" t="n">
-        <v>8817800</v>
+        <v>11971800</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45852</v>
+        <v>45860</v>
       </c>
       <c r="B13" t="n">
-        <v>226.1686859130859</v>
+        <v>232.0338439941406</v>
       </c>
       <c r="C13" t="n">
-        <v>227.3357863025809</v>
+        <v>235.3966472031473</v>
       </c>
       <c r="D13" t="n">
-        <v>223.8345002259765</v>
+        <v>229.2248977425589</v>
       </c>
       <c r="E13" t="n">
-        <v>226.821470109318</v>
+        <v>235.2285085518851</v>
       </c>
       <c r="F13" t="n">
-        <v>10673500</v>
+        <v>11919500</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45853</v>
+        <v>45861</v>
       </c>
       <c r="B14" t="n">
-        <v>234.3581237792969</v>
+        <v>237.7011566162109</v>
       </c>
       <c r="C14" t="n">
-        <v>235.1098201921258</v>
+        <v>237.8692952633755</v>
       </c>
       <c r="D14" t="n">
-        <v>231.2920421272182</v>
+        <v>233.794366635459</v>
       </c>
       <c r="E14" t="n">
-        <v>231.8953702571503</v>
+        <v>235.9109576819443</v>
       </c>
       <c r="F14" t="n">
-        <v>14270100</v>
+        <v>9885400</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45854</v>
+        <v>45862</v>
       </c>
       <c r="B15" t="n">
-        <v>234.9614410400391</v>
+        <v>238.957275390625</v>
       </c>
       <c r="C15" t="n">
-        <v>235.7032371445645</v>
+        <v>239.3034378763647</v>
       </c>
       <c r="D15" t="n">
-        <v>231.5887377960789</v>
+        <v>235.4263184296621</v>
       </c>
       <c r="E15" t="n">
-        <v>233.8141261096551</v>
+        <v>237.5824804462792</v>
       </c>
       <c r="F15" t="n">
-        <v>15092800</v>
+        <v>9081900</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45855</v>
+        <v>45863</v>
       </c>
       <c r="B16" t="n">
         <v>242.9135131835938</v>
       </c>
       <c r="C16" t="n">
-        <v>245.5641907894646</v>
+        <v>243.5465119470764</v>
       </c>
       <c r="D16" t="n">
-        <v>238.7495575810806</v>
+        <v>238.3044829194239</v>
       </c>
       <c r="E16" t="n">
-        <v>243.1014221935387</v>
+        <v>238.6803311230758</v>
       </c>
       <c r="F16" t="n">
-        <v>27395700</v>
+        <v>11593400</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45856</v>
+        <v>45866</v>
       </c>
       <c r="B17" t="n">
-        <v>237.7704010009766</v>
+        <v>240.0946807861328</v>
       </c>
       <c r="C17" t="n">
-        <v>243.2794813199559</v>
+        <v>241.2815515759682</v>
       </c>
       <c r="D17" t="n">
-        <v>236.0791141278278</v>
+        <v>238.4132792428759</v>
       </c>
       <c r="E17" t="n">
-        <v>242.6266970463031</v>
+        <v>240.3419461628436</v>
       </c>
       <c r="F17" t="n">
-        <v>16252000</v>
+        <v>11892200</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45859</v>
+        <v>45867</v>
       </c>
       <c r="B18" t="n">
-        <v>236.2373504638672</v>
+        <v>238.6902313232422</v>
       </c>
       <c r="C18" t="n">
-        <v>239.6891655153443</v>
+        <v>241.3013532733822</v>
       </c>
       <c r="D18" t="n">
-        <v>236.0988824545226</v>
+        <v>237.1967537804632</v>
       </c>
       <c r="E18" t="n">
-        <v>237.4934477301073</v>
+        <v>238.8583699796969</v>
       </c>
       <c r="F18" t="n">
-        <v>11971800</v>
+        <v>9411500</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45860</v>
+        <v>45868</v>
       </c>
       <c r="B19" t="n">
-        <v>232.0338439941406</v>
+        <v>240.2529296875</v>
       </c>
       <c r="C19" t="n">
-        <v>235.3966472031473</v>
+        <v>241.8947753797364</v>
       </c>
       <c r="D19" t="n">
-        <v>229.2248977425589</v>
+        <v>238.5814133579722</v>
       </c>
       <c r="E19" t="n">
-        <v>235.2285085518851</v>
+        <v>239.4715626604769</v>
       </c>
       <c r="F19" t="n">
-        <v>11919500</v>
+        <v>6823800</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45861</v>
+        <v>45869</v>
       </c>
       <c r="B20" t="n">
-        <v>237.7011566162109</v>
+        <v>238.9770355224609</v>
       </c>
       <c r="C20" t="n">
-        <v>237.8692952633755</v>
+        <v>244.7037100762124</v>
       </c>
       <c r="D20" t="n">
-        <v>233.794366635459</v>
+        <v>237.1769514348016</v>
       </c>
       <c r="E20" t="n">
-        <v>235.9109576819443</v>
+        <v>243.2893442791621</v>
       </c>
       <c r="F20" t="n">
-        <v>9885400</v>
+        <v>13490700</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45862</v>
+        <v>45870</v>
       </c>
       <c r="B21" t="n">
-        <v>238.9572601318359</v>
+        <v>232.6371765136719</v>
       </c>
       <c r="C21" t="n">
-        <v>239.3034225954712</v>
+        <v>234.5955141796546</v>
       </c>
       <c r="D21" t="n">
-        <v>235.4263033963448</v>
+        <v>229.30402878904</v>
       </c>
       <c r="E21" t="n">
-        <v>237.5824652752787</v>
+        <v>233.0426802840443</v>
       </c>
       <c r="F21" t="n">
-        <v>9081900</v>
+        <v>13549800</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45863</v>
+        <v>45873</v>
       </c>
       <c r="B22" t="n">
-        <v>242.9135131835938</v>
+        <v>236.3856964111328</v>
       </c>
       <c r="C22" t="n">
-        <v>243.5465119470764</v>
+        <v>236.3856964111328</v>
       </c>
       <c r="D22" t="n">
-        <v>238.3044829194239</v>
+        <v>233.804245315269</v>
       </c>
       <c r="E22" t="n">
-        <v>238.6803311230758</v>
+        <v>235.3076230077108</v>
       </c>
       <c r="F22" t="n">
-        <v>11593400</v>
+        <v>6450700</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45866</v>
+        <v>45874</v>
       </c>
       <c r="B23" t="n">
-        <v>240.0946807861328</v>
+        <v>229.9271392822266</v>
       </c>
       <c r="C23" t="n">
-        <v>241.2815515759682</v>
+        <v>236.019762040258</v>
       </c>
       <c r="D23" t="n">
-        <v>238.4132792428759</v>
+        <v>227.6522947033383</v>
       </c>
       <c r="E23" t="n">
-        <v>240.3419461628436</v>
+        <v>235.7230405574671</v>
       </c>
       <c r="F23" t="n">
-        <v>11892200</v>
+        <v>11868900</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45867</v>
+        <v>45875</v>
       </c>
       <c r="B24" t="n">
-        <v>238.6902160644531</v>
+        <v>228.8391571044922</v>
       </c>
       <c r="C24" t="n">
-        <v>241.3013378476716</v>
+        <v>229.660079970128</v>
       </c>
       <c r="D24" t="n">
-        <v>237.1967386171479</v>
+        <v>226.3170623234721</v>
       </c>
       <c r="E24" t="n">
-        <v>238.8583547101592</v>
+        <v>228.502879812607</v>
       </c>
       <c r="F24" t="n">
-        <v>9411500</v>
+        <v>9457200</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45868</v>
+        <v>45876</v>
       </c>
       <c r="B25" t="n">
-        <v>240.2529296875</v>
+        <v>239.9660949707031</v>
       </c>
       <c r="C25" t="n">
-        <v>241.8947753797364</v>
+        <v>245.1289971794407</v>
       </c>
       <c r="D25" t="n">
-        <v>238.5814133579722</v>
+        <v>238.1660108984572</v>
       </c>
       <c r="E25" t="n">
-        <v>239.4715626604769</v>
+        <v>241.7958647723148</v>
       </c>
       <c r="F25" t="n">
-        <v>6823800</v>
+        <v>17691000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45869</v>
+        <v>45877</v>
       </c>
       <c r="B26" t="n">
-        <v>238.9770355224609</v>
+        <v>239.1847381591797</v>
       </c>
       <c r="C26" t="n">
-        <v>244.7037100762124</v>
+        <v>240.5001917311243</v>
       </c>
       <c r="D26" t="n">
-        <v>237.1769514348016</v>
+        <v>236.3560217387914</v>
       </c>
       <c r="E26" t="n">
-        <v>243.2893442791621</v>
+        <v>240.5001917311243</v>
       </c>
       <c r="F26" t="n">
-        <v>13490700</v>
+        <v>10552500</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45870</v>
+        <v>45880</v>
       </c>
       <c r="B27" t="n">
-        <v>232.6371612548828</v>
+        <v>239.4419097900391</v>
       </c>
       <c r="C27" t="n">
-        <v>234.5954987924172</v>
+        <v>242.6662601391793</v>
       </c>
       <c r="D27" t="n">
-        <v>229.3040137488738</v>
+        <v>238.8979229128637</v>
       </c>
       <c r="E27" t="n">
-        <v>233.042664998658</v>
+        <v>239.3924536935901</v>
       </c>
       <c r="F27" t="n">
-        <v>13549800</v>
+        <v>8272900</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45873</v>
+        <v>45881</v>
       </c>
       <c r="B28" t="n">
-        <v>236.3857269287109</v>
+        <v>241.6178283691406</v>
       </c>
       <c r="C28" t="n">
-        <v>236.3857269287109</v>
+        <v>242.0925887576028</v>
       </c>
       <c r="D28" t="n">
-        <v>233.8042754995798</v>
+        <v>239.0561626937391</v>
       </c>
       <c r="E28" t="n">
-        <v>235.3076533861088</v>
+        <v>241.0540711591781</v>
       </c>
       <c r="F28" t="n">
-        <v>6450700</v>
+        <v>7295800</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45874</v>
+        <v>45882</v>
       </c>
       <c r="B29" t="n">
-        <v>229.9271392822266</v>
+        <v>238.7990264892578</v>
       </c>
       <c r="C29" t="n">
-        <v>236.019762040258</v>
+        <v>243.7344340361031</v>
       </c>
       <c r="D29" t="n">
-        <v>227.6522947033383</v>
+        <v>237.3154341428701</v>
       </c>
       <c r="E29" t="n">
-        <v>235.7230405574671</v>
+        <v>243.7344340361031</v>
       </c>
       <c r="F29" t="n">
-        <v>11868900</v>
+        <v>7971900</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45875</v>
+        <v>45883</v>
       </c>
       <c r="B30" t="n">
-        <v>228.8391723632812</v>
+        <v>238.3638305664062</v>
       </c>
       <c r="C30" t="n">
-        <v>229.6600952836554</v>
+        <v>238.7396787801039</v>
       </c>
       <c r="D30" t="n">
-        <v>226.3170774140901</v>
+        <v>234.2295605832579</v>
       </c>
       <c r="E30" t="n">
-        <v>228.5028950489734</v>
+        <v>235.3669753147684</v>
       </c>
       <c r="F30" t="n">
-        <v>9457200</v>
+        <v>11040500</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45876</v>
+        <v>45884</v>
       </c>
       <c r="B31" t="n">
-        <v>239.9661102294922</v>
+        <v>236.2670135498047</v>
       </c>
       <c r="C31" t="n">
-        <v>245.1290127665246</v>
+        <v>238.1660097994922</v>
       </c>
       <c r="D31" t="n">
-        <v>238.1660260427838</v>
+        <v>234.6647236735991</v>
       </c>
       <c r="E31" t="n">
-        <v>241.7958801474539</v>
+        <v>237.701149691863</v>
       </c>
       <c r="F31" t="n">
-        <v>17691000</v>
+        <v>8155500</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45877</v>
+        <v>45887</v>
       </c>
       <c r="B32" t="n">
-        <v>239.1847381591797</v>
+        <v>238.7693328857422</v>
       </c>
       <c r="C32" t="n">
-        <v>240.5001917311243</v>
+        <v>240.2034689976107</v>
       </c>
       <c r="D32" t="n">
-        <v>236.3560217387914</v>
+        <v>237.3648674105972</v>
       </c>
       <c r="E32" t="n">
-        <v>240.5001917311243</v>
+        <v>237.3648674105972</v>
       </c>
       <c r="F32" t="n">
-        <v>10552500</v>
+        <v>6919800</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45880</v>
+        <v>45888</v>
       </c>
       <c r="B33" t="n">
-        <v>239.44189453125</v>
+        <v>230.1546020507812</v>
       </c>
       <c r="C33" t="n">
-        <v>242.6662446749137</v>
+        <v>237.5428924711381</v>
       </c>
       <c r="D33" t="n">
-        <v>238.897907688741</v>
+        <v>230.0359195032672</v>
       </c>
       <c r="E33" t="n">
-        <v>239.3924384379527</v>
+        <v>237.3945392867456</v>
       </c>
       <c r="F33" t="n">
-        <v>8272900</v>
+        <v>14594700</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45881</v>
+        <v>45889</v>
       </c>
       <c r="B34" t="n">
-        <v>241.6178283691406</v>
+        <v>226.0994567871094</v>
       </c>
       <c r="C34" t="n">
-        <v>242.0925887576028</v>
+        <v>226.5247459726773</v>
       </c>
       <c r="D34" t="n">
-        <v>239.0561626937391</v>
+        <v>221.2530465566674</v>
       </c>
       <c r="E34" t="n">
-        <v>241.0540711591781</v>
+        <v>225.6444818730812</v>
       </c>
       <c r="F34" t="n">
-        <v>7295800</v>
+        <v>17165200</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45882</v>
+        <v>45890</v>
       </c>
       <c r="B35" t="n">
-        <v>238.7990264892578</v>
+        <v>224.8433685302734</v>
       </c>
       <c r="C35" t="n">
-        <v>243.7344340361031</v>
+        <v>227.8105532404205</v>
       </c>
       <c r="D35" t="n">
-        <v>237.3154341428701</v>
+        <v>223.7850654062177</v>
       </c>
       <c r="E35" t="n">
-        <v>243.7344340361031</v>
+        <v>225.6543911699351</v>
       </c>
       <c r="F35" t="n">
-        <v>7971900</v>
+        <v>7449100</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45883</v>
+        <v>45891</v>
       </c>
       <c r="B36" t="n">
-        <v>238.3638305664062</v>
+        <v>230.4414367675781</v>
       </c>
       <c r="C36" t="n">
-        <v>238.7396787801039</v>
+        <v>231.885458058811</v>
       </c>
       <c r="D36" t="n">
-        <v>234.2295605832579</v>
+        <v>223.6960303144911</v>
       </c>
       <c r="E36" t="n">
-        <v>235.3669753147684</v>
+        <v>225.506014611212</v>
       </c>
       <c r="F36" t="n">
-        <v>11040500</v>
+        <v>10299500</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45884</v>
+        <v>45894</v>
       </c>
       <c r="B37" t="n">
-        <v>236.2670288085938</v>
+        <v>233.0130004882812</v>
       </c>
       <c r="C37" t="n">
-        <v>238.1660251809238</v>
+        <v>234.6845168761834</v>
       </c>
       <c r="D37" t="n">
-        <v>234.6647388289078</v>
+        <v>229.7095386248346</v>
       </c>
       <c r="E37" t="n">
-        <v>237.7011650432727</v>
+        <v>231.7371177645495</v>
       </c>
       <c r="F37" t="n">
-        <v>8155500</v>
+        <v>7655000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45887</v>
+        <v>45895</v>
       </c>
       <c r="B38" t="n">
-        <v>238.7693328857422</v>
+        <v>236.1087493896484</v>
       </c>
       <c r="C38" t="n">
-        <v>240.2034689976107</v>
+        <v>236.2175467522883</v>
       </c>
       <c r="D38" t="n">
-        <v>237.3648674105972</v>
+        <v>233.1514502356221</v>
       </c>
       <c r="E38" t="n">
-        <v>237.3648674105972</v>
+        <v>233.7844489568324</v>
       </c>
       <c r="F38" t="n">
-        <v>6919800</v>
+        <v>9793100</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45888</v>
+        <v>45896</v>
       </c>
       <c r="B39" t="n">
-        <v>230.1546173095703</v>
+        <v>236.6725158691406</v>
       </c>
       <c r="C39" t="n">
-        <v>237.5429082197561</v>
+        <v>236.7813132360573</v>
       </c>
       <c r="D39" t="n">
-        <v>230.0359347541878</v>
+        <v>232.8646382108174</v>
       </c>
       <c r="E39" t="n">
-        <v>237.394555025528</v>
+        <v>234.2789888888539</v>
       </c>
       <c r="F39" t="n">
-        <v>14594700</v>
+        <v>9516400</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45889</v>
+        <v>45897</v>
       </c>
       <c r="B40" t="n">
-        <v>226.0994873046875</v>
+        <v>235.6636962890625</v>
       </c>
       <c r="C40" t="n">
-        <v>226.5247765476584</v>
+        <v>238.0275527552297</v>
       </c>
       <c r="D40" t="n">
-        <v>221.2530764201055</v>
+        <v>233.4185223777531</v>
       </c>
       <c r="E40" t="n">
-        <v>225.6445123292494</v>
+        <v>233.7152438567791</v>
       </c>
       <c r="F40" t="n">
-        <v>17165200</v>
+        <v>8466200</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45890</v>
+        <v>45898</v>
       </c>
       <c r="B41" t="n">
-        <v>224.8433685302734</v>
+        <v>228.3446197509766</v>
       </c>
       <c r="C41" t="n">
-        <v>227.8105532404205</v>
+        <v>233.3690538956459</v>
       </c>
       <c r="D41" t="n">
-        <v>223.7850654062177</v>
+        <v>228.0577985613338</v>
       </c>
       <c r="E41" t="n">
-        <v>225.6543911699351</v>
+        <v>233.2602565288406</v>
       </c>
       <c r="F41" t="n">
-        <v>7449100</v>
+        <v>15526000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45891</v>
+        <v>45902</v>
       </c>
       <c r="B42" t="n">
-        <v>230.4414520263672</v>
+        <v>225.8917388916016</v>
       </c>
       <c r="C42" t="n">
-        <v>231.8854734132166</v>
+        <v>226.8313442296358</v>
       </c>
       <c r="D42" t="n">
-        <v>223.6960451266299</v>
+        <v>223.1619347839498</v>
       </c>
       <c r="E42" t="n">
-        <v>225.5060295431997</v>
+        <v>223.6762358602525</v>
       </c>
       <c r="F42" t="n">
-        <v>10299500</v>
+        <v>13974900</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45894</v>
+        <v>45903</v>
       </c>
       <c r="B43" t="n">
-        <v>233.0129852294922</v>
+        <v>228.8589477539062</v>
       </c>
       <c r="C43" t="n">
-        <v>234.6845015079356</v>
+        <v>229.9073505652696</v>
       </c>
       <c r="D43" t="n">
-        <v>229.7095235823718</v>
+        <v>226.0994727144099</v>
       </c>
       <c r="E43" t="n">
-        <v>231.7371025893112</v>
+        <v>228.9875305827313</v>
       </c>
       <c r="F43" t="n">
-        <v>7655000</v>
+        <v>7198500</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45895</v>
+        <v>45904</v>
       </c>
       <c r="B44" t="n">
-        <v>236.1087646484375</v>
+        <v>232.6371765136719</v>
       </c>
       <c r="C44" t="n">
-        <v>236.2175620181086</v>
+        <v>232.7360736146898</v>
       </c>
       <c r="D44" t="n">
-        <v>233.1514653032925</v>
+        <v>227.780880624805</v>
       </c>
       <c r="E44" t="n">
-        <v>233.784464065411</v>
+        <v>228.8193982827243</v>
       </c>
       <c r="F44" t="n">
-        <v>9793100</v>
+        <v>6241900</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45896</v>
+        <v>45905</v>
       </c>
       <c r="B45" t="n">
-        <v>236.6725158691406</v>
+        <v>240.7474822998047</v>
       </c>
       <c r="C45" t="n">
-        <v>236.7813132360573</v>
+        <v>241.8750118949406</v>
       </c>
       <c r="D45" t="n">
-        <v>232.8646382108174</v>
+        <v>235.297743346746</v>
       </c>
       <c r="E45" t="n">
-        <v>234.2789888888539</v>
+        <v>237.612158908873</v>
       </c>
       <c r="F45" t="n">
-        <v>9516400</v>
+        <v>14056600</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45897</v>
+        <v>45908</v>
       </c>
       <c r="B46" t="n">
-        <v>235.6636810302734</v>
+        <v>244.4861297607422</v>
       </c>
       <c r="C46" t="n">
-        <v>238.0275373433853</v>
+        <v>245.1685846527634</v>
       </c>
       <c r="D46" t="n">
-        <v>233.4185072643349</v>
+        <v>238.9770496200111</v>
       </c>
       <c r="E46" t="n">
-        <v>233.7152287241487</v>
+        <v>239.3430126601841</v>
       </c>
       <c r="F46" t="n">
-        <v>8466200</v>
+        <v>12986600</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45898</v>
+        <v>45909</v>
       </c>
       <c r="B47" t="n">
-        <v>228.3446197509766</v>
+        <v>248.1753234863281</v>
       </c>
       <c r="C47" t="n">
-        <v>233.3690538956459</v>
+        <v>251.943645594913</v>
       </c>
       <c r="D47" t="n">
-        <v>228.0577985613338</v>
+        <v>244.2289624501245</v>
       </c>
       <c r="E47" t="n">
-        <v>233.2602565288406</v>
+        <v>244.2289624501245</v>
       </c>
       <c r="F47" t="n">
-        <v>15526000</v>
+        <v>13443400</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45902</v>
+        <v>45910</v>
       </c>
       <c r="B48" t="n">
-        <v>225.8917694091797</v>
+        <v>257.5911865234375</v>
       </c>
       <c r="C48" t="n">
-        <v>226.8313748741529</v>
+        <v>261.685885549929</v>
       </c>
       <c r="D48" t="n">
-        <v>223.1619649327362</v>
+        <v>254.9306086009324</v>
       </c>
       <c r="E48" t="n">
-        <v>223.6762660785201</v>
+        <v>256.0383526818429</v>
       </c>
       <c r="F48" t="n">
-        <v>13974900</v>
+        <v>18822400</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45903</v>
+        <v>45911</v>
       </c>
       <c r="B49" t="n">
-        <v>228.8589477539062</v>
+        <v>256.0779113769531</v>
       </c>
       <c r="C49" t="n">
-        <v>229.9073505652696</v>
+        <v>258.7780600831707</v>
       </c>
       <c r="D49" t="n">
-        <v>226.0994727144099</v>
+        <v>255.4053568147395</v>
       </c>
       <c r="E49" t="n">
-        <v>228.9875305827313</v>
+        <v>257.5021623226766</v>
       </c>
       <c r="F49" t="n">
-        <v>7198500</v>
+        <v>10005000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45904</v>
+        <v>45912</v>
       </c>
       <c r="B50" t="n">
-        <v>232.6371612548828</v>
+        <v>256.4933166503906</v>
       </c>
       <c r="C50" t="n">
-        <v>232.736058349414</v>
+        <v>258.0956217043181</v>
       </c>
       <c r="D50" t="n">
-        <v>227.7808656845428</v>
+        <v>255.5537262948531</v>
       </c>
       <c r="E50" t="n">
-        <v>228.8193832743452</v>
+        <v>257.9967095132713</v>
       </c>
       <c r="F50" t="n">
-        <v>6241900</v>
+        <v>8496600</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45905</v>
+        <v>45915</v>
       </c>
       <c r="B51" t="n">
-        <v>240.7474670410156</v>
+        <v>258.5209350585938</v>
       </c>
       <c r="C51" t="n">
-        <v>241.8749965646877</v>
+        <v>259.9253856777809</v>
       </c>
       <c r="D51" t="n">
-        <v>235.2977284333662</v>
+        <v>255.9196981284078</v>
       </c>
       <c r="E51" t="n">
-        <v>237.6121438488035</v>
+        <v>257.1560251725064</v>
       </c>
       <c r="F51" t="n">
-        <v>14056600</v>
+        <v>8147700</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45908</v>
+        <v>45916</v>
       </c>
       <c r="B52" t="n">
-        <v>244.4861145019531</v>
+        <v>260.0111389160156</v>
       </c>
       <c r="C52" t="n">
-        <v>245.1685693513812</v>
+        <v>264.3568996908289</v>
       </c>
       <c r="D52" t="n">
-        <v>238.9770347050529</v>
+        <v>258.5724633115559</v>
       </c>
       <c r="E52" t="n">
-        <v>239.3429977223855</v>
+        <v>263.8409760972693</v>
       </c>
       <c r="F52" t="n">
-        <v>12986600</v>
+        <v>10381900</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45909</v>
+        <v>45917</v>
       </c>
       <c r="B53" t="n">
-        <v>248.1753082275391</v>
+        <v>260.7354431152344</v>
       </c>
       <c r="C53" t="n">
-        <v>251.9436301044328</v>
+        <v>262.7396392925697</v>
       </c>
       <c r="D53" t="n">
-        <v>244.2289474339731</v>
+        <v>257.6993694692491</v>
       </c>
       <c r="E53" t="n">
-        <v>244.2289474339731</v>
+        <v>262.2733126722264</v>
       </c>
       <c r="F53" t="n">
-        <v>13443400</v>
+        <v>10422000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45910</v>
+        <v>45918</v>
       </c>
       <c r="B54" t="n">
-        <v>257.5911865234375</v>
+        <v>266.5397338867188</v>
       </c>
       <c r="C54" t="n">
-        <v>261.685885549929</v>
+        <v>268.4248732551709</v>
       </c>
       <c r="D54" t="n">
-        <v>254.9306086009324</v>
+        <v>255.9630722413997</v>
       </c>
       <c r="E54" t="n">
-        <v>256.0383526818429</v>
+        <v>255.9829049770096</v>
       </c>
       <c r="F54" t="n">
-        <v>18822400</v>
+        <v>16917300</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45911</v>
+        <v>45919</v>
       </c>
       <c r="B55" t="n">
-        <v>256.0779418945312</v>
+        <v>262.7991943359375</v>
       </c>
       <c r="C55" t="n">
-        <v>258.7780909225337</v>
+        <v>264.4859155448514</v>
       </c>
       <c r="D55" t="n">
-        <v>255.4053872521673</v>
+        <v>260.7553022050341</v>
       </c>
       <c r="E55" t="n">
-        <v>257.502193009987</v>
+        <v>264.2874670688664</v>
       </c>
       <c r="F55" t="n">
-        <v>10005000</v>
+        <v>17640200</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45912</v>
+        <v>45922</v>
       </c>
       <c r="B56" t="n">
-        <v>256.4933166503906</v>
+        <v>270.49853515625</v>
       </c>
       <c r="C56" t="n">
-        <v>258.0956217043181</v>
+        <v>274.199353976218</v>
       </c>
       <c r="D56" t="n">
-        <v>255.5537262948531</v>
+        <v>263.3746769365127</v>
       </c>
       <c r="E56" t="n">
-        <v>257.9967095132713</v>
+        <v>264.456151489733</v>
       </c>
       <c r="F56" t="n">
-        <v>8496600</v>
+        <v>15630300</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45915</v>
+        <v>45923</v>
       </c>
       <c r="B57" t="n">
-        <v>258.5209045410156</v>
+        <v>280.4996948242188</v>
       </c>
       <c r="C57" t="n">
-        <v>259.9253549944119</v>
+        <v>283.7639812686768</v>
       </c>
       <c r="D57" t="n">
-        <v>255.9196679178974</v>
+        <v>277.8108907525507</v>
       </c>
       <c r="E57" t="n">
-        <v>257.1559948160515</v>
+        <v>280.1921209032043</v>
       </c>
       <c r="F57" t="n">
-        <v>8147700</v>
+        <v>17830300</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>45916</v>
+        <v>45924</v>
       </c>
       <c r="B58" t="n">
-        <v>260.0111389160156</v>
+        <v>278.5153503417969</v>
       </c>
       <c r="C58" t="n">
-        <v>264.3568996908289</v>
+        <v>279.0114412520244</v>
       </c>
       <c r="D58" t="n">
-        <v>258.5724633115559</v>
+        <v>274.5565545674572</v>
       </c>
       <c r="E58" t="n">
-        <v>263.8409760972693</v>
+        <v>278.1184836694121</v>
       </c>
       <c r="F58" t="n">
-        <v>10381900</v>
+        <v>10231000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>45917</v>
+        <v>45925</v>
       </c>
       <c r="B59" t="n">
-        <v>260.7354431152344</v>
+        <v>274.4970092773438</v>
       </c>
       <c r="C59" t="n">
-        <v>262.7396392925697</v>
+        <v>274.9732674224433</v>
       </c>
       <c r="D59" t="n">
-        <v>257.6993694692491</v>
+        <v>268.0775920808023</v>
       </c>
       <c r="E59" t="n">
-        <v>262.2733126722264</v>
+        <v>270.9846773698227</v>
       </c>
       <c r="F59" t="n">
-        <v>10422000</v>
+        <v>11863400</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>45918</v>
+        <v>45926</v>
       </c>
       <c r="B60" t="n">
-        <v>266.5397338867188</v>
+        <v>271.2227783203125</v>
       </c>
       <c r="C60" t="n">
-        <v>268.4248732551709</v>
+        <v>273.3460617183889</v>
       </c>
       <c r="D60" t="n">
-        <v>255.9630722413997</v>
+        <v>268.5042101180865</v>
       </c>
       <c r="E60" t="n">
-        <v>255.9829049770096</v>
+        <v>271.7486636956161</v>
       </c>
       <c r="F60" t="n">
-        <v>16917300</v>
+        <v>10451900</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>45919</v>
+        <v>45929</v>
       </c>
       <c r="B61" t="n">
-        <v>262.7991943359375</v>
+        <v>271.0938415527344</v>
       </c>
       <c r="C61" t="n">
-        <v>264.4859155448514</v>
+        <v>277.6819128974079</v>
       </c>
       <c r="D61" t="n">
-        <v>260.7553022050341</v>
+        <v>271.0938415527344</v>
       </c>
       <c r="E61" t="n">
-        <v>264.2874670688664</v>
+        <v>274.3283336004599</v>
       </c>
       <c r="F61" t="n">
-        <v>17640200</v>
+        <v>8046200</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>45922</v>
+        <v>45930</v>
       </c>
       <c r="B62" t="n">
-        <v>270.49853515625</v>
+        <v>277.1064758300781</v>
       </c>
       <c r="C62" t="n">
-        <v>274.199353976218</v>
+        <v>277.304894031587</v>
       </c>
       <c r="D62" t="n">
-        <v>263.3746769365127</v>
+        <v>271.6891411582071</v>
       </c>
       <c r="E62" t="n">
-        <v>264.456151489733</v>
+        <v>273.1675126962315</v>
       </c>
       <c r="F62" t="n">
-        <v>15630300</v>
+        <v>8348800</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>45923</v>
+        <v>45931</v>
       </c>
       <c r="B63" t="n">
-        <v>280.4996948242188</v>
+        <v>286.2146911621094</v>
       </c>
       <c r="C63" t="n">
-        <v>283.7639812686768</v>
+        <v>288.208986311923</v>
       </c>
       <c r="D63" t="n">
-        <v>277.8108907525507</v>
+        <v>275.0030486945597</v>
       </c>
       <c r="E63" t="n">
-        <v>280.1921209032043</v>
+        <v>276.2631087070019</v>
       </c>
       <c r="F63" t="n">
-        <v>17830300</v>
+        <v>14620100</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>45924</v>
+        <v>45932</v>
       </c>
       <c r="B64" t="n">
-        <v>278.5153503417969</v>
+        <v>285.8574829101562</v>
       </c>
       <c r="C64" t="n">
-        <v>279.0114412520244</v>
+        <v>294.400183924721</v>
       </c>
       <c r="D64" t="n">
-        <v>274.5565545674572</v>
+        <v>284.7859398924857</v>
       </c>
       <c r="E64" t="n">
-        <v>278.1184836694121</v>
+        <v>294.201735453789</v>
       </c>
       <c r="F64" t="n">
-        <v>10231000</v>
+        <v>10198000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>45925</v>
+        <v>45933</v>
       </c>
       <c r="B65" t="n">
-        <v>274.4970092773438</v>
+        <v>289.9056091308594</v>
       </c>
       <c r="C65" t="n">
-        <v>274.9732674224433</v>
+        <v>293.7453479391941</v>
       </c>
       <c r="D65" t="n">
-        <v>268.0775920808023</v>
+        <v>288.2188879210599</v>
       </c>
       <c r="E65" t="n">
-        <v>270.9846773698227</v>
+        <v>290.5703539956843</v>
       </c>
       <c r="F65" t="n">
-        <v>11863400</v>
+        <v>10572500</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>45926</v>
+        <v>45936</v>
       </c>
       <c r="B66" t="n">
-        <v>271.2227783203125</v>
+        <v>300.0357666015625</v>
       </c>
       <c r="C66" t="n">
-        <v>273.3460617183889</v>
+        <v>304.8974513064171</v>
       </c>
       <c r="D66" t="n">
-        <v>268.5042101180865</v>
+        <v>297.5950078814736</v>
       </c>
       <c r="E66" t="n">
-        <v>271.7486636956161</v>
+        <v>297.6644678735823</v>
       </c>
       <c r="F66" t="n">
-        <v>10451900</v>
+        <v>15785000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>45929</v>
+        <v>45937</v>
       </c>
       <c r="B67" t="n">
-        <v>271.0938415527344</v>
+        <v>291.731201171875</v>
       </c>
       <c r="C67" t="n">
-        <v>277.6819128974079</v>
+        <v>304.6990240193715</v>
       </c>
       <c r="D67" t="n">
-        <v>271.0938415527344</v>
+        <v>290.9870648531753</v>
       </c>
       <c r="E67" t="n">
-        <v>274.3283336004599</v>
+        <v>304.2227658749694</v>
       </c>
       <c r="F67" t="n">
-        <v>8046200</v>
+        <v>13081000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>45930</v>
+        <v>45938</v>
       </c>
       <c r="B68" t="n">
-        <v>277.1064758300781</v>
+        <v>302.13916015625</v>
       </c>
       <c r="C68" t="n">
-        <v>277.304894031587</v>
+        <v>304.0044665954838</v>
       </c>
       <c r="D68" t="n">
-        <v>271.6891411582071</v>
+        <v>291.6815868469853</v>
       </c>
       <c r="E68" t="n">
-        <v>273.1675126962315</v>
+        <v>292.6936012797901</v>
       </c>
       <c r="F68" t="n">
-        <v>8348800</v>
+        <v>12821200</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>45931</v>
+        <v>45939</v>
       </c>
       <c r="B69" t="n">
-        <v>286.2146911621094</v>
+        <v>297.5354614257812</v>
       </c>
       <c r="C69" t="n">
-        <v>288.208986311923</v>
+        <v>300.4623793558781</v>
       </c>
       <c r="D69" t="n">
-        <v>275.0030486945597</v>
+        <v>295.0947028531109</v>
       </c>
       <c r="E69" t="n">
-        <v>276.2631087070019</v>
+        <v>299.9464557577721</v>
       </c>
       <c r="F69" t="n">
-        <v>14620100</v>
+        <v>10259900</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>45932</v>
+        <v>45940</v>
       </c>
       <c r="B70" t="n">
-        <v>285.8574829101562</v>
+        <v>278.4657287597656</v>
       </c>
       <c r="C70" t="n">
-        <v>294.400183924721</v>
+        <v>297.8529682966983</v>
       </c>
       <c r="D70" t="n">
-        <v>284.7859398924857</v>
+        <v>278.1382918317124</v>
       </c>
       <c r="E70" t="n">
-        <v>294.201735453789</v>
+        <v>297.6148240911186</v>
       </c>
       <c r="F70" t="n">
-        <v>10198000</v>
+        <v>23398000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>45933</v>
+        <v>45943</v>
       </c>
       <c r="B71" t="n">
-        <v>289.9056091308594</v>
+        <v>300.52197265625</v>
       </c>
       <c r="C71" t="n">
-        <v>293.7453479391941</v>
+        <v>302.2483593720482</v>
       </c>
       <c r="D71" t="n">
-        <v>288.2188879210599</v>
+        <v>290.0346033193896</v>
       </c>
       <c r="E71" t="n">
-        <v>290.5703539956843</v>
+        <v>295.9083028677765</v>
       </c>
       <c r="F71" t="n">
-        <v>10572500</v>
+        <v>20318300</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>45936</v>
+        <v>45944</v>
       </c>
       <c r="B72" t="n">
-        <v>300.0357666015625</v>
+        <v>293.6262512207031</v>
       </c>
       <c r="C72" t="n">
-        <v>304.8974513064171</v>
+        <v>299.3908244066789</v>
       </c>
       <c r="D72" t="n">
-        <v>297.5950078814736</v>
+        <v>289.0622093993036</v>
       </c>
       <c r="E72" t="n">
-        <v>297.6644678735823</v>
+        <v>293.3186773196876</v>
       </c>
       <c r="F72" t="n">
-        <v>15785000</v>
+        <v>16567900</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>45937</v>
+        <v>45945</v>
       </c>
       <c r="B73" t="n">
-        <v>291.731201171875</v>
+        <v>302.3277282714844</v>
       </c>
       <c r="C73" t="n">
-        <v>304.6990240193715</v>
+        <v>304.2128677633362</v>
       </c>
       <c r="D73" t="n">
-        <v>290.9870648531753</v>
+        <v>297.7240201528247</v>
       </c>
       <c r="E73" t="n">
-        <v>304.2227658749694</v>
+        <v>303.895392577868</v>
       </c>
       <c r="F73" t="n">
-        <v>13081000</v>
+        <v>20788000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>45938</v>
+        <v>45946</v>
       </c>
       <c r="B74" t="n">
-        <v>302.13916015625</v>
+        <v>297.4957580566406</v>
       </c>
       <c r="C74" t="n">
-        <v>304.0044665954838</v>
+        <v>308.9356118757877</v>
       </c>
       <c r="D74" t="n">
-        <v>291.6815868469853</v>
+        <v>294.3703917494307</v>
       </c>
       <c r="E74" t="n">
-        <v>292.6936012797901</v>
+        <v>308.4990495043508</v>
       </c>
       <c r="F74" t="n">
-        <v>12821200</v>
+        <v>26341500</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>45939</v>
+        <v>45947</v>
       </c>
       <c r="B75" t="n">
-        <v>297.5354614257812</v>
+        <v>292.7729797363281</v>
       </c>
       <c r="C75" t="n">
-        <v>300.4623793558781</v>
+        <v>300.928714995697</v>
       </c>
       <c r="D75" t="n">
-        <v>295.0947028531109</v>
+        <v>292.614257300604</v>
       </c>
       <c r="E75" t="n">
-        <v>299.9464557577721</v>
+        <v>296.0670304388142</v>
       </c>
       <c r="F75" t="n">
-        <v>10259900</v>
+        <v>17633300</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>45940</v>
+        <v>45950</v>
       </c>
       <c r="B76" t="n">
-        <v>278.4657287597656</v>
+        <v>295.3725280761719</v>
       </c>
       <c r="C76" t="n">
-        <v>297.8529682966983</v>
+        <v>301.2759915009516</v>
       </c>
       <c r="D76" t="n">
-        <v>278.1382918317124</v>
+        <v>294.7375172029331</v>
       </c>
       <c r="E76" t="n">
-        <v>297.6148240911186</v>
+        <v>297.6545340590304</v>
       </c>
       <c r="F76" t="n">
-        <v>23398000</v>
+        <v>13391600</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>45943</v>
+        <v>45951</v>
       </c>
       <c r="B77" t="n">
-        <v>300.52197265625</v>
+        <v>292.2074584960938</v>
       </c>
       <c r="C77" t="n">
-        <v>302.2483593720482</v>
+        <v>297.0294472938208</v>
       </c>
       <c r="D77" t="n">
-        <v>290.0346033193896</v>
+        <v>291.3640979481377</v>
       </c>
       <c r="E77" t="n">
-        <v>295.9083028677765</v>
+        <v>296.6623448889301</v>
       </c>
       <c r="F77" t="n">
-        <v>20318300</v>
+        <v>11190500</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>45944</v>
+        <v>45952</v>
       </c>
       <c r="B78" t="n">
-        <v>293.6262512207031</v>
+        <v>286.6214599609375</v>
       </c>
       <c r="C78" t="n">
-        <v>299.3908244066789</v>
+        <v>292.8920556948521</v>
       </c>
       <c r="D78" t="n">
-        <v>289.0622093993036</v>
+        <v>282.176474957343</v>
       </c>
       <c r="E78" t="n">
-        <v>293.3186773196876</v>
+        <v>290.7092438004568</v>
       </c>
       <c r="F78" t="n">
-        <v>16567900</v>
+        <v>15409100</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>45945</v>
+        <v>45953</v>
       </c>
       <c r="B79" t="n">
-        <v>302.3277282714844</v>
+        <v>288.45703125</v>
       </c>
       <c r="C79" t="n">
-        <v>304.2128677633362</v>
+        <v>291.7907476292175</v>
       </c>
       <c r="D79" t="n">
-        <v>297.7240201528247</v>
+        <v>287.3656251928801</v>
       </c>
       <c r="E79" t="n">
-        <v>303.895392577868</v>
+        <v>287.5342791459432</v>
       </c>
       <c r="F79" t="n">
-        <v>20788000</v>
+        <v>10379900</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>45946</v>
+        <v>45954</v>
       </c>
       <c r="B80" t="n">
-        <v>297.4957580566406</v>
+        <v>292.6539306640625</v>
       </c>
       <c r="C80" t="n">
-        <v>308.9356118757877</v>
+        <v>295.6205747892861</v>
       </c>
       <c r="D80" t="n">
-        <v>294.3703917494307</v>
+        <v>292.0884100589532</v>
       </c>
       <c r="E80" t="n">
-        <v>308.4990495043508</v>
+        <v>293.2591772976509</v>
       </c>
       <c r="F80" t="n">
-        <v>26341500</v>
+        <v>8747000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>45947</v>
+        <v>45957</v>
       </c>
       <c r="B81" t="n">
-        <v>292.7729797363281</v>
+        <v>295.9182434082031</v>
       </c>
       <c r="C81" t="n">
-        <v>300.928714995697</v>
+        <v>298.1308198838283</v>
       </c>
       <c r="D81" t="n">
-        <v>292.614257300604</v>
+        <v>291.3938964929148</v>
       </c>
       <c r="E81" t="n">
-        <v>296.0670304388142</v>
+        <v>296.3151101013185</v>
       </c>
       <c r="F81" t="n">
-        <v>17633300</v>
+        <v>13615000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>45950</v>
+        <v>45958</v>
       </c>
       <c r="B82" t="n">
-        <v>295.3725280761719</v>
+        <v>299.1725463867188</v>
       </c>
       <c r="C82" t="n">
-        <v>301.2759915009516</v>
+        <v>299.7678614617131</v>
       </c>
       <c r="D82" t="n">
-        <v>294.7375172029331</v>
+        <v>293.765144017412</v>
       </c>
       <c r="E82" t="n">
-        <v>297.6545340590304</v>
+        <v>295.9876516121254</v>
       </c>
       <c r="F82" t="n">
-        <v>13391600</v>
+        <v>11804200</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>45951</v>
+        <v>45959</v>
       </c>
       <c r="B83" t="n">
-        <v>292.2074584960938</v>
+        <v>302.7047424316406</v>
       </c>
       <c r="C83" t="n">
-        <v>297.0294472938208</v>
+        <v>305.5522993596172</v>
       </c>
       <c r="D83" t="n">
-        <v>291.3640979481377</v>
+        <v>300.0159382255111</v>
       </c>
       <c r="E83" t="n">
-        <v>296.6623448889301</v>
+        <v>303.4091830331609</v>
       </c>
       <c r="F83" t="n">
-        <v>11190500</v>
+        <v>16177300</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>45952</v>
+        <v>45960</v>
       </c>
       <c r="B84" t="n">
-        <v>286.6214599609375</v>
+        <v>300.8493347167969</v>
       </c>
       <c r="C84" t="n">
-        <v>292.8920556948521</v>
+        <v>304.907354215164</v>
       </c>
       <c r="D84" t="n">
-        <v>282.176474957343</v>
+        <v>298.468104705007</v>
       </c>
       <c r="E84" t="n">
-        <v>290.7092438004568</v>
+        <v>300.7104147456095</v>
       </c>
       <c r="F84" t="n">
-        <v>15409100</v>
+        <v>14507100</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>45953</v>
+        <v>45961</v>
       </c>
       <c r="B85" t="n">
-        <v>288.45703125</v>
+        <v>298.0811462402344</v>
       </c>
       <c r="C85" t="n">
-        <v>291.7907476292175</v>
+        <v>305.274463694973</v>
       </c>
       <c r="D85" t="n">
-        <v>287.3656251928801</v>
+        <v>294.3604647981282</v>
       </c>
       <c r="E85" t="n">
-        <v>287.5342791459432</v>
+        <v>303.5976741694118</v>
       </c>
       <c r="F85" t="n">
-        <v>10379900</v>
+        <v>12667900</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>45954</v>
+        <v>45964</v>
       </c>
       <c r="B86" t="n">
-        <v>292.6539306640625</v>
+        <v>302.4765014648438</v>
       </c>
       <c r="C86" t="n">
-        <v>295.6205747892861</v>
+        <v>307.6953869467885</v>
       </c>
       <c r="D86" t="n">
-        <v>292.0884100589532</v>
+        <v>299.7579332697235</v>
       </c>
       <c r="E86" t="n">
-        <v>293.2591772976509</v>
+        <v>300.2242598844103</v>
       </c>
       <c r="F86" t="n">
-        <v>8747000</v>
+        <v>12466600</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>45957</v>
+        <v>45965</v>
       </c>
       <c r="B87" t="n">
-        <v>295.9182434082031</v>
+        <v>291.7510681152344</v>
       </c>
       <c r="C87" t="n">
-        <v>298.1308198838283</v>
+        <v>299.6289946218963</v>
       </c>
       <c r="D87" t="n">
-        <v>291.3938964929148</v>
+        <v>291.2153117038204</v>
       </c>
       <c r="E87" t="n">
-        <v>296.3151101013185</v>
+        <v>294.5589597765923</v>
       </c>
       <c r="F87" t="n">
-        <v>13615000</v>
+        <v>16224300</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>45958</v>
+        <v>45966</v>
       </c>
       <c r="B88" t="n">
-        <v>299.1725463867188</v>
+        <v>291.3442687988281</v>
       </c>
       <c r="C88" t="n">
-        <v>299.7678614617131</v>
+        <v>295.8884479721017</v>
       </c>
       <c r="D88" t="n">
-        <v>293.765144017412</v>
+        <v>289.2209852820558</v>
       </c>
       <c r="E88" t="n">
-        <v>295.9876516121254</v>
+        <v>290.3322240172327</v>
       </c>
       <c r="F88" t="n">
-        <v>11804200</v>
+        <v>10502500</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>45959</v>
+        <v>45967</v>
       </c>
       <c r="B89" t="n">
-        <v>302.7047424316406</v>
+        <v>286.9786376953125</v>
       </c>
       <c r="C89" t="n">
-        <v>305.5522993596172</v>
+        <v>292.3364433314327</v>
       </c>
       <c r="D89" t="n">
-        <v>300.0159382255111</v>
+        <v>285.1331941869922</v>
       </c>
       <c r="E89" t="n">
-        <v>303.4091830331609</v>
+        <v>291.8006567120239</v>
       </c>
       <c r="F89" t="n">
-        <v>16177300</v>
+        <v>11516900</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>45960</v>
+        <v>45968</v>
       </c>
       <c r="B90" t="n">
-        <v>300.8493347167969</v>
+        <v>284.2600708007812</v>
       </c>
       <c r="C90" t="n">
-        <v>304.907354215164</v>
+        <v>285.6392179644077</v>
       </c>
       <c r="D90" t="n">
-        <v>298.468104705007</v>
+        <v>274.9633326666985</v>
       </c>
       <c r="E90" t="n">
-        <v>300.7104147456095</v>
+        <v>282.9801478677512</v>
       </c>
       <c r="F90" t="n">
-        <v>14507100</v>
+        <v>15715700</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>45961</v>
+        <v>45971</v>
       </c>
       <c r="B91" t="n">
-        <v>298.0811462402344</v>
+        <v>292.9614868164062</v>
       </c>
       <c r="C91" t="n">
-        <v>305.274463694973</v>
+        <v>294.8069605685671</v>
       </c>
       <c r="D91" t="n">
-        <v>294.3604647981282</v>
+        <v>289.4690180475096</v>
       </c>
       <c r="E91" t="n">
-        <v>303.5976741694118</v>
+        <v>292.0585978138683</v>
       </c>
       <c r="F91" t="n">
-        <v>12667900</v>
+        <v>10869200</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>45964</v>
+        <v>45972</v>
       </c>
       <c r="B92" t="n">
-        <v>302.4765014648438</v>
+        <v>288.8935546875</v>
       </c>
       <c r="C92" t="n">
-        <v>307.6953869467885</v>
+        <v>292.6142360080955</v>
       </c>
       <c r="D92" t="n">
-        <v>299.7579332697235</v>
+        <v>286.6512143890135</v>
       </c>
       <c r="E92" t="n">
-        <v>300.2242598844103</v>
+        <v>289.7765806425173</v>
       </c>
       <c r="F92" t="n">
-        <v>12466600</v>
+        <v>9666300</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>45965</v>
+        <v>45973</v>
       </c>
       <c r="B93" t="n">
-        <v>291.7510681152344</v>
+        <v>288.3478698730469</v>
       </c>
       <c r="C93" t="n">
-        <v>299.6289946218963</v>
+        <v>292.5646425230715</v>
       </c>
       <c r="D93" t="n">
-        <v>291.2153117038204</v>
+        <v>287.3159923229249</v>
       </c>
       <c r="E93" t="n">
-        <v>294.5589597765923</v>
+        <v>291.4038067732967</v>
       </c>
       <c r="F93" t="n">
-        <v>16224300</v>
+        <v>9715900</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>45966</v>
+        <v>45974</v>
       </c>
       <c r="B94" t="n">
-        <v>291.3442687988281</v>
+        <v>279.9937133789062</v>
       </c>
       <c r="C94" t="n">
-        <v>295.8884479721017</v>
+        <v>287.2366283376572</v>
       </c>
       <c r="D94" t="n">
-        <v>289.2209852820558</v>
+        <v>277.810901328304</v>
       </c>
       <c r="E94" t="n">
-        <v>290.3322240172327</v>
+        <v>286.9092216695595</v>
       </c>
       <c r="F94" t="n">
-        <v>10502500</v>
+        <v>13827600</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>45967</v>
+        <v>45975</v>
       </c>
       <c r="B95" t="n">
-        <v>286.9786376953125</v>
+        <v>282.5932006835938</v>
       </c>
       <c r="C95" t="n">
-        <v>292.3364433314327</v>
+        <v>284.6172295623482</v>
       </c>
       <c r="D95" t="n">
-        <v>285.1331941869922</v>
+        <v>271.0938183480427</v>
       </c>
       <c r="E95" t="n">
-        <v>291.8006567120239</v>
+        <v>273.752858052355</v>
       </c>
       <c r="F95" t="n">
-        <v>11516900</v>
+        <v>11486800</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>45968</v>
+        <v>45978</v>
       </c>
       <c r="B96" t="n">
-        <v>284.2600708007812</v>
+        <v>279.8052062988281</v>
       </c>
       <c r="C96" t="n">
-        <v>285.6392179644077</v>
+        <v>284.2898572496578</v>
       </c>
       <c r="D96" t="n">
-        <v>274.9633326666985</v>
+        <v>277.6124626636006</v>
       </c>
       <c r="E96" t="n">
-        <v>282.9801478677512</v>
+        <v>279.2396553913358</v>
       </c>
       <c r="F96" t="n">
-        <v>15715700</v>
+        <v>10227100</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>45971</v>
+        <v>45979</v>
       </c>
       <c r="B97" t="n">
-        <v>292.9614868164062</v>
+        <v>275.7372436523438</v>
       </c>
       <c r="C97" t="n">
-        <v>294.8069605685671</v>
+        <v>277.999416912211</v>
       </c>
       <c r="D97" t="n">
-        <v>289.4690180475096</v>
+        <v>270.5878177630827</v>
       </c>
       <c r="E97" t="n">
-        <v>292.0585978138683</v>
+        <v>275.3800424644778</v>
       </c>
       <c r="F97" t="n">
-        <v>10869200</v>
+        <v>11850400</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>45972</v>
+        <v>45980</v>
       </c>
       <c r="B98" t="n">
-        <v>288.8935546875</v>
+        <v>280.1623840332031</v>
       </c>
       <c r="C98" t="n">
-        <v>292.6142360080955</v>
+        <v>282.3253331984228</v>
       </c>
       <c r="D98" t="n">
-        <v>286.6512143890135</v>
+        <v>274.1596959545832</v>
       </c>
       <c r="E98" t="n">
-        <v>289.7765806425173</v>
+        <v>274.755011120154</v>
       </c>
       <c r="F98" t="n">
-        <v>9666300</v>
+        <v>11179200</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>45973</v>
+        <v>45981</v>
       </c>
       <c r="B99" t="n">
-        <v>288.3478698730469</v>
+        <v>275.3304443359375</v>
       </c>
       <c r="C99" t="n">
-        <v>292.5646425230715</v>
+        <v>290.5604407360827</v>
       </c>
       <c r="D99" t="n">
-        <v>287.3159923229249</v>
+        <v>274.2489698276997</v>
       </c>
       <c r="E99" t="n">
-        <v>291.4038067732967</v>
+        <v>289.9254298620799</v>
       </c>
       <c r="F99" t="n">
-        <v>9715900</v>
+        <v>15747300</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>45974</v>
+        <v>45982</v>
       </c>
       <c r="B100" t="n">
-        <v>279.9937133789062</v>
+        <v>272.9094848632812</v>
       </c>
       <c r="C100" t="n">
-        <v>287.2366283376572</v>
+        <v>276.5111091322138</v>
       </c>
       <c r="D100" t="n">
-        <v>277.810901328304</v>
+        <v>264.7339176775704</v>
       </c>
       <c r="E100" t="n">
-        <v>286.9092216695595</v>
+        <v>270.6770761292138</v>
       </c>
       <c r="F100" t="n">
-        <v>13827600</v>
+        <v>20872800</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>45975</v>
+        <v>45985</v>
       </c>
       <c r="B101" t="n">
-        <v>282.5932006835938</v>
+        <v>282.4146423339844</v>
       </c>
       <c r="C101" t="n">
-        <v>284.6172295623482</v>
+        <v>282.8313417341185</v>
       </c>
       <c r="D101" t="n">
-        <v>271.0938183480427</v>
+        <v>271.0541486024111</v>
       </c>
       <c r="E101" t="n">
-        <v>273.752858052355</v>
+        <v>271.0541486024111</v>
       </c>
       <c r="F101" t="n">
-        <v>11486800</v>
+        <v>13570300</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>45978</v>
+        <v>45986</v>
       </c>
       <c r="B102" t="n">
-        <v>279.8052062988281</v>
+        <v>282.4543151855469</v>
       </c>
       <c r="C102" t="n">
-        <v>284.2898572496578</v>
+        <v>283.168687312</v>
       </c>
       <c r="D102" t="n">
-        <v>277.6124626636006</v>
+        <v>270.9449999389071</v>
       </c>
       <c r="E102" t="n">
-        <v>279.2396553913358</v>
+        <v>280.519578790685</v>
       </c>
       <c r="F102" t="n">
-        <v>10227100</v>
+        <v>13726800</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>45979</v>
+        <v>45987</v>
       </c>
       <c r="B103" t="n">
-        <v>275.7372436523438</v>
+        <v>287.6930236816406</v>
       </c>
       <c r="C103" t="n">
-        <v>277.999416912211</v>
+        <v>290.5207478421946</v>
       </c>
       <c r="D103" t="n">
-        <v>270.5878177630827</v>
+        <v>285.4804776659429</v>
       </c>
       <c r="E103" t="n">
-        <v>275.3800424644778</v>
+        <v>286.8397618751708</v>
       </c>
       <c r="F103" t="n">
-        <v>11850400</v>
+        <v>12220300</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>45980</v>
+        <v>45989</v>
       </c>
       <c r="B104" t="n">
-        <v>280.1623840332031</v>
+        <v>289.2308959960938</v>
       </c>
       <c r="C104" t="n">
-        <v>282.3253331984228</v>
+        <v>290.3818303973529</v>
       </c>
       <c r="D104" t="n">
-        <v>274.1596959545832</v>
+        <v>286.7405102489479</v>
       </c>
       <c r="E104" t="n">
-        <v>274.755011120154</v>
+        <v>290.1933134527253</v>
       </c>
       <c r="F104" t="n">
-        <v>11179200</v>
+        <v>5515400</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>45981</v>
+        <v>45992</v>
       </c>
       <c r="B105" t="n">
-        <v>275.3304443359375</v>
+        <v>285.4308471679688</v>
       </c>
       <c r="C105" t="n">
-        <v>290.5604407360827</v>
+        <v>288.8836506623742</v>
       </c>
       <c r="D105" t="n">
-        <v>274.2489698276997</v>
+        <v>280.9759606655977</v>
       </c>
       <c r="E105" t="n">
-        <v>289.9254298620799</v>
+        <v>284.6768096049723</v>
       </c>
       <c r="F105" t="n">
-        <v>15747300</v>
+        <v>7713000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>45982</v>
+        <v>45993</v>
       </c>
       <c r="B106" t="n">
-        <v>272.9094848632812</v>
+        <v>289.8063659667969</v>
       </c>
       <c r="C106" t="n">
-        <v>276.5111091322138</v>
+        <v>292.1975276362799</v>
       </c>
       <c r="D106" t="n">
-        <v>264.7339176775704</v>
+        <v>286.9191134184747</v>
       </c>
       <c r="E106" t="n">
-        <v>270.6770761292138</v>
+        <v>289.7170732420839</v>
       </c>
       <c r="F106" t="n">
-        <v>20872800</v>
+        <v>10746400</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>45985</v>
+        <v>45994</v>
       </c>
       <c r="B107" t="n">
-        <v>282.4146423339844</v>
+        <v>293.14013671875</v>
       </c>
       <c r="C107" t="n">
-        <v>282.8313417341185</v>
+        <v>294.3009725152348</v>
       </c>
       <c r="D107" t="n">
-        <v>271.0541486024111</v>
+        <v>283.8334662155739</v>
       </c>
       <c r="E107" t="n">
-        <v>271.0541486024111</v>
+        <v>289.8956827236291</v>
       </c>
       <c r="F107" t="n">
-        <v>13570300</v>
+        <v>9599200</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>45986</v>
+        <v>45995</v>
       </c>
       <c r="B108" t="n">
-        <v>282.4543151855469</v>
+        <v>290.6398010253906</v>
       </c>
       <c r="C108" t="n">
-        <v>283.168687312</v>
+        <v>291.7312070372234</v>
       </c>
       <c r="D108" t="n">
-        <v>270.9449999389071</v>
+        <v>287.9311641494156</v>
       </c>
       <c r="E108" t="n">
-        <v>280.519578790685</v>
+        <v>291.6816100599067</v>
       </c>
       <c r="F108" t="n">
-        <v>13726800</v>
+        <v>6753000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>45987</v>
+        <v>45996</v>
       </c>
       <c r="B109" t="n">
-        <v>287.6930236816406</v>
+        <v>292.4158020019531</v>
       </c>
       <c r="C109" t="n">
-        <v>290.5207478421946</v>
+        <v>298.4482536249387</v>
       </c>
       <c r="D109" t="n">
-        <v>285.4804776659429</v>
+        <v>290.957293641084</v>
       </c>
       <c r="E109" t="n">
-        <v>286.8397618751708</v>
+        <v>293.7353903860806</v>
       </c>
       <c r="F109" t="n">
-        <v>12220300</v>
+        <v>10275300</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>45989</v>
+        <v>45999</v>
       </c>
       <c r="B110" t="n">
-        <v>289.2308959960938</v>
+        <v>299.5098876953125</v>
       </c>
       <c r="C110" t="n">
-        <v>290.3818303973529</v>
+        <v>300.2540239771721</v>
       </c>
       <c r="D110" t="n">
-        <v>286.7405102489479</v>
+        <v>294.4001579490064</v>
       </c>
       <c r="E110" t="n">
-        <v>290.1933134527253</v>
+        <v>298.8451429064149</v>
       </c>
       <c r="F110" t="n">
-        <v>5515400</v>
+        <v>16643100</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>45992</v>
+        <v>46000</v>
       </c>
       <c r="B111" t="n">
-        <v>285.4308471679688</v>
+        <v>301.0378723144531</v>
       </c>
       <c r="C111" t="n">
-        <v>288.8836506623742</v>
+        <v>302.2979322528996</v>
       </c>
       <c r="D111" t="n">
-        <v>280.9759606655977</v>
+        <v>296.1662562251443</v>
       </c>
       <c r="E111" t="n">
-        <v>284.6768096049723</v>
+        <v>297.6445973625877</v>
       </c>
       <c r="F111" t="n">
-        <v>7713000</v>
+        <v>11349100</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>45993</v>
+        <v>46001</v>
       </c>
       <c r="B112" t="n">
-        <v>289.8063659667969</v>
+        <v>307.7153015136719</v>
       </c>
       <c r="C112" t="n">
-        <v>292.1975276362799</v>
+        <v>311.5252762835024</v>
       </c>
       <c r="D112" t="n">
-        <v>286.9191134184747</v>
+        <v>300.135017448174</v>
       </c>
       <c r="E112" t="n">
-        <v>289.7170732420839</v>
+        <v>302.9825745872591</v>
       </c>
       <c r="F112" t="n">
-        <v>10746400</v>
+        <v>12429200</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>45994</v>
+        <v>46002</v>
       </c>
       <c r="B113" t="n">
-        <v>293.14013671875</v>
+        <v>303.2831726074219</v>
       </c>
       <c r="C113" t="n">
-        <v>294.3009725152348</v>
+        <v>304.2680746022398</v>
       </c>
       <c r="D113" t="n">
-        <v>283.8334662155739</v>
+        <v>298.0999588756921</v>
       </c>
       <c r="E113" t="n">
-        <v>289.8956827236291</v>
+        <v>303.7507581691417</v>
       </c>
       <c r="F113" t="n">
-        <v>9599200</v>
+        <v>15028400</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>45995</v>
+        <v>46003</v>
       </c>
       <c r="B114" t="n">
-        <v>290.6398010253906</v>
+        <v>290.5390014648438</v>
       </c>
       <c r="C114" t="n">
-        <v>291.7312070372234</v>
+        <v>302.7160814421844</v>
       </c>
       <c r="D114" t="n">
-        <v>287.9311641494156</v>
+        <v>289.4844520085434</v>
       </c>
       <c r="E114" t="n">
-        <v>291.6816100599067</v>
+        <v>302.7160814421844</v>
       </c>
       <c r="F114" t="n">
-        <v>6753000</v>
+        <v>19306100</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>45996</v>
+        <v>46006</v>
       </c>
       <c r="B115" t="n">
-        <v>292.4158020019531</v>
+        <v>286.2610778808594</v>
       </c>
       <c r="C115" t="n">
-        <v>298.4482536249387</v>
+        <v>294.2796490463091</v>
       </c>
       <c r="D115" t="n">
-        <v>290.957293641084</v>
+        <v>286.0720520049891</v>
       </c>
       <c r="E115" t="n">
-        <v>293.7353903860806</v>
+        <v>293.6329959576229</v>
       </c>
       <c r="F115" t="n">
-        <v>10275300</v>
+        <v>12082400</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>45999</v>
+        <v>46007</v>
       </c>
       <c r="B116" t="n">
-        <v>299.5098876953125</v>
+        <v>285.3955688476562</v>
       </c>
       <c r="C116" t="n">
-        <v>300.2540239771721</v>
+        <v>286.9773930782894</v>
       </c>
       <c r="D116" t="n">
-        <v>294.4001579490064</v>
+        <v>281.8638269338228</v>
       </c>
       <c r="E116" t="n">
-        <v>298.8451429064149</v>
+        <v>285.7835789370498</v>
       </c>
       <c r="F116" t="n">
-        <v>16643100</v>
+        <v>11418400</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>46000</v>
+        <v>46008</v>
       </c>
       <c r="B117" t="n">
-        <v>301.0378723144531</v>
+        <v>275.5364990234375</v>
       </c>
       <c r="C117" t="n">
-        <v>302.2979322528996</v>
+        <v>287.614117587584</v>
       </c>
       <c r="D117" t="n">
-        <v>296.1662562251443</v>
+        <v>273.6661568096194</v>
       </c>
       <c r="E117" t="n">
-        <v>297.6445973625877</v>
+        <v>287.0470399324042</v>
       </c>
       <c r="F117" t="n">
-        <v>11349100</v>
+        <v>16823000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>46001</v>
+        <v>46009</v>
       </c>
       <c r="B118" t="n">
-        <v>307.7153015136719</v>
+        <v>283.2168273925781</v>
       </c>
       <c r="C118" t="n">
-        <v>311.5252762835024</v>
+        <v>285.6840919054254</v>
       </c>
       <c r="D118" t="n">
-        <v>300.135017448174</v>
+        <v>280.3018939540933</v>
       </c>
       <c r="E118" t="n">
-        <v>302.9825745872591</v>
+        <v>283.5351899801831</v>
       </c>
       <c r="F118" t="n">
-        <v>12429200</v>
+        <v>11260300</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>46002</v>
+        <v>46010</v>
       </c>
       <c r="B119" t="n">
-        <v>303.2831726074219</v>
+        <v>287.4648742675781</v>
       </c>
       <c r="C119" t="n">
-        <v>304.2680746022398</v>
+        <v>290.6683254077278</v>
       </c>
       <c r="D119" t="n">
-        <v>298.0999588756921</v>
+        <v>284.9080762017799</v>
       </c>
       <c r="E119" t="n">
-        <v>303.7507581691417</v>
+        <v>284.9080762017799</v>
       </c>
       <c r="F119" t="n">
-        <v>15028400</v>
+        <v>12735800</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>46003</v>
+        <v>46013</v>
       </c>
       <c r="B120" t="n">
-        <v>290.5390014648438</v>
+        <v>291.7726440429688</v>
       </c>
       <c r="C120" t="n">
-        <v>302.7160814421844</v>
+        <v>293.4937633890043</v>
       </c>
       <c r="D120" t="n">
-        <v>289.4844520085434</v>
+        <v>289.7132758191229</v>
       </c>
       <c r="E120" t="n">
-        <v>302.7160814421844</v>
+        <v>293.1555145111942</v>
       </c>
       <c r="F120" t="n">
-        <v>19306100</v>
+        <v>6091100</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46006</v>
+        <v>46014</v>
       </c>
       <c r="B121" t="n">
-        <v>286.2610778808594</v>
+        <v>295.4237670898438</v>
       </c>
       <c r="C121" t="n">
-        <v>294.2796490463091</v>
+        <v>296.3788244408282</v>
       </c>
       <c r="D121" t="n">
-        <v>286.0720520049891</v>
+        <v>290.6981808430299</v>
       </c>
       <c r="E121" t="n">
-        <v>293.6329959576229</v>
+        <v>291.891994941579</v>
       </c>
       <c r="F121" t="n">
-        <v>12082400</v>
+        <v>6802300</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46007</v>
+        <v>46015</v>
       </c>
       <c r="B122" t="n">
-        <v>285.3955688476562</v>
+        <v>297.2642517089844</v>
       </c>
       <c r="C122" t="n">
-        <v>286.9773930782894</v>
+        <v>297.6224172120486</v>
       </c>
       <c r="D122" t="n">
-        <v>281.8638269338228</v>
+        <v>294.7074837586965</v>
       </c>
       <c r="E122" t="n">
-        <v>285.7835789370498</v>
+        <v>296.2097021978008</v>
       </c>
       <c r="F122" t="n">
-        <v>11418400</v>
+        <v>2753900</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46008</v>
+        <v>46017</v>
       </c>
       <c r="B123" t="n">
-        <v>275.5364990234375</v>
+        <v>301.2834777832031</v>
       </c>
       <c r="C123" t="n">
-        <v>287.614117587584</v>
+        <v>301.82071082512</v>
       </c>
       <c r="D123" t="n">
-        <v>273.6661568096194</v>
+        <v>296.9856741693193</v>
       </c>
       <c r="E123" t="n">
-        <v>287.0470399324042</v>
+        <v>298.3585861871483</v>
       </c>
       <c r="F123" t="n">
-        <v>16823000</v>
+        <v>5125900</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46009</v>
+        <v>46020</v>
       </c>
       <c r="B124" t="n">
-        <v>283.2168273925781</v>
+        <v>299.3733825683594</v>
       </c>
       <c r="C124" t="n">
-        <v>285.6840919054254</v>
+        <v>302.9349691756451</v>
       </c>
       <c r="D124" t="n">
-        <v>280.3018939540933</v>
+        <v>297.1150301981547</v>
       </c>
       <c r="E124" t="n">
-        <v>283.5351899801831</v>
+        <v>300.228947875312</v>
       </c>
       <c r="F124" t="n">
-        <v>11260300</v>
+        <v>6205100</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>46010</v>
+        <v>46021</v>
       </c>
       <c r="B125" t="n">
-        <v>287.4648742675781</v>
+        <v>298.0402526855469</v>
       </c>
       <c r="C125" t="n">
-        <v>290.6683254077278</v>
+        <v>302.9847098791469</v>
       </c>
       <c r="D125" t="n">
-        <v>284.9080762017799</v>
+        <v>297.9109463420213</v>
       </c>
       <c r="E125" t="n">
-        <v>284.9080762017799</v>
+        <v>300.8059632663079</v>
       </c>
       <c r="F125" t="n">
-        <v>12735800</v>
+        <v>6190600</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>46013</v>
+        <v>46022</v>
       </c>
       <c r="B126" t="n">
-        <v>291.7726440429688</v>
+        <v>302.328125</v>
       </c>
       <c r="C126" t="n">
-        <v>293.4937633890043</v>
+        <v>305.8101362096284</v>
       </c>
       <c r="D126" t="n">
-        <v>289.7132758191229</v>
+        <v>301.8704673812959</v>
       </c>
       <c r="E126" t="n">
-        <v>293.1555145111942</v>
+        <v>302.4375450648673</v>
       </c>
       <c r="F126" t="n">
-        <v>6091100</v>
+        <v>8175100</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>46014</v>
+        <v>46024</v>
       </c>
       <c r="B127" t="n">
-        <v>295.4237670898438</v>
+        <v>317.96728515625</v>
       </c>
       <c r="C127" t="n">
-        <v>296.3788244408282</v>
+        <v>319.9371194754431</v>
       </c>
       <c r="D127" t="n">
-        <v>290.6981808430299</v>
+        <v>310.0979669193405</v>
       </c>
       <c r="E127" t="n">
-        <v>291.891994941579</v>
+        <v>310.3765265882512</v>
       </c>
       <c r="F127" t="n">
-        <v>6802300</v>
+        <v>18526900</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>46015</v>
+        <v>46027</v>
       </c>
       <c r="B128" t="n">
-        <v>297.2642517089844</v>
+        <v>320.5937194824219</v>
       </c>
       <c r="C128" t="n">
-        <v>297.6224172120486</v>
+        <v>329.5474618418999</v>
       </c>
       <c r="D128" t="n">
-        <v>294.7074837586965</v>
+        <v>319.8475742857987</v>
       </c>
       <c r="E128" t="n">
-        <v>296.2097021978008</v>
+        <v>328.7018245469152</v>
       </c>
       <c r="F128" t="n">
-        <v>2753900</v>
+        <v>17446300</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>46017</v>
+        <v>46028</v>
       </c>
       <c r="B129" t="n">
-        <v>301.2834777832031</v>
+        <v>325.7471008300781</v>
       </c>
       <c r="C129" t="n">
-        <v>301.82071082512</v>
+        <v>331.3680554544452</v>
       </c>
       <c r="D129" t="n">
-        <v>296.9856741693193</v>
+        <v>322.9217012206051</v>
       </c>
       <c r="E129" t="n">
-        <v>298.3585861871483</v>
+        <v>328.5227695688286</v>
       </c>
       <c r="F129" t="n">
-        <v>5125900</v>
+        <v>15599600</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>46020</v>
+        <v>46029</v>
       </c>
       <c r="B130" t="n">
-        <v>299.3733825683594</v>
+        <v>317.0420532226562</v>
       </c>
       <c r="C130" t="n">
-        <v>302.9349691756451</v>
+        <v>324.6228833752338</v>
       </c>
       <c r="D130" t="n">
-        <v>297.1150301981547</v>
+        <v>316.9027885769733</v>
       </c>
       <c r="E130" t="n">
-        <v>300.228947875312</v>
+        <v>323.0012866910015</v>
       </c>
       <c r="F130" t="n">
-        <v>6205100</v>
+        <v>11744800</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>46021</v>
+        <v>46030</v>
       </c>
       <c r="B131" t="n">
-        <v>298.0402526855469</v>
+        <v>316.3755493164062</v>
       </c>
       <c r="C131" t="n">
-        <v>302.9847098791469</v>
+        <v>322.8321832662991</v>
       </c>
       <c r="D131" t="n">
-        <v>297.9109463420213</v>
+        <v>314.5151653214018</v>
       </c>
       <c r="E131" t="n">
-        <v>300.8059632663079</v>
+        <v>322.7227632010534</v>
       </c>
       <c r="F131" t="n">
-        <v>6190600</v>
+        <v>10850800</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>46022</v>
+        <v>46031</v>
       </c>
       <c r="B132" t="n">
-        <v>302.328125</v>
+        <v>321.9666442871094</v>
       </c>
       <c r="C132" t="n">
-        <v>305.8101362096284</v>
+        <v>323.1007692434349</v>
       </c>
       <c r="D132" t="n">
-        <v>301.8704673812959</v>
+        <v>316.6142910064096</v>
       </c>
       <c r="E132" t="n">
-        <v>302.4375450648673</v>
+        <v>318.186156924328</v>
       </c>
       <c r="F132" t="n">
-        <v>8175100</v>
+        <v>12325100</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>46024</v>
+        <v>46034</v>
       </c>
       <c r="B133" t="n">
-        <v>317.96728515625</v>
+        <v>330.0647888183594</v>
       </c>
       <c r="C133" t="n">
-        <v>319.9371194754431</v>
+        <v>331.8356389272924</v>
       </c>
       <c r="D133" t="n">
-        <v>310.0979669193405</v>
+        <v>319.4098435703697</v>
       </c>
       <c r="E133" t="n">
-        <v>310.3765265882512</v>
+        <v>320.4445067771578</v>
       </c>
       <c r="F133" t="n">
-        <v>18526900</v>
+        <v>12714800</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>46027</v>
+        <v>46035</v>
       </c>
       <c r="B134" t="n">
-        <v>320.5937194824219</v>
+        <v>329.5076599121094</v>
       </c>
       <c r="C134" t="n">
-        <v>329.5474618418999</v>
+        <v>334.6909037531499</v>
       </c>
       <c r="D134" t="n">
-        <v>319.8475742857987</v>
+        <v>329.0798772846784</v>
       </c>
       <c r="E134" t="n">
-        <v>328.7018245469152</v>
+        <v>331.1591315955093</v>
       </c>
       <c r="F134" t="n">
-        <v>17446300</v>
+        <v>11473600</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>46028</v>
+        <v>46036</v>
       </c>
       <c r="B135" t="n">
-        <v>325.7471008300781</v>
+        <v>325.4287414550781</v>
       </c>
       <c r="C135" t="n">
-        <v>331.3680554544452</v>
+        <v>328.164607307781</v>
       </c>
       <c r="D135" t="n">
-        <v>322.9217012206051</v>
+        <v>323.1505332047328</v>
       </c>
       <c r="E135" t="n">
-        <v>328.5227695688286</v>
+        <v>328.164607307781</v>
       </c>
       <c r="F135" t="n">
-        <v>15599600</v>
+        <v>11210800</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>46029</v>
+        <v>46037</v>
       </c>
       <c r="B136" t="n">
-        <v>317.0420532226562</v>
+        <v>339.8840942382812</v>
       </c>
       <c r="C136" t="n">
-        <v>324.6228833752338</v>
+        <v>349.5242628055195</v>
       </c>
       <c r="D136" t="n">
-        <v>316.9027885769733</v>
+        <v>336.1832126341018</v>
       </c>
       <c r="E136" t="n">
-        <v>323.0012866910015</v>
+        <v>341.0480638104695</v>
       </c>
       <c r="F136" t="n">
-        <v>11744800</v>
+        <v>42188500</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>46030</v>
+        <v>46038</v>
       </c>
       <c r="B137" t="n">
-        <v>316.3755493164062</v>
+        <v>340.64013671875</v>
       </c>
       <c r="C137" t="n">
-        <v>322.8321832662991</v>
+        <v>348.0518575773862</v>
       </c>
       <c r="D137" t="n">
-        <v>314.5151653214018</v>
+        <v>339.7049656735853</v>
       </c>
       <c r="E137" t="n">
-        <v>322.7227632010534</v>
+        <v>344.7290280520938</v>
       </c>
       <c r="F137" t="n">
-        <v>10850800</v>
+        <v>18246100</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>46031</v>
+        <v>46042</v>
       </c>
       <c r="B138" t="n">
-        <v>321.9666442871094</v>
+        <v>325.4784851074219</v>
       </c>
       <c r="C138" t="n">
-        <v>323.1007692434349</v>
+        <v>340.3914306345235</v>
       </c>
       <c r="D138" t="n">
-        <v>316.6142910064096</v>
+        <v>325.2198117253413</v>
       </c>
       <c r="E138" t="n">
-        <v>318.186156924328</v>
+        <v>339.0384352590497</v>
       </c>
       <c r="F138" t="n">
-        <v>12325100</v>
+        <v>22809900</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>46034</v>
+        <v>46043</v>
       </c>
       <c r="B139" t="n">
-        <v>330.0647888183594</v>
+        <v>324.44384765625</v>
       </c>
       <c r="C139" t="n">
-        <v>331.8356389272924</v>
+        <v>331.9252168077863</v>
       </c>
       <c r="D139" t="n">
-        <v>319.4098435703697</v>
+        <v>324.0061066799057</v>
       </c>
       <c r="E139" t="n">
-        <v>320.4445067771578</v>
+        <v>331.7162742776711</v>
       </c>
       <c r="F139" t="n">
-        <v>12714800</v>
+        <v>16789800</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>46035</v>
+        <v>46044</v>
       </c>
       <c r="B140" t="n">
-        <v>329.5076599121094</v>
+        <v>325.6874084472656</v>
       </c>
       <c r="C140" t="n">
-        <v>334.6909037531499</v>
+        <v>333.327928191825</v>
       </c>
       <c r="D140" t="n">
-        <v>329.0798772846784</v>
+        <v>325.2198228962958</v>
       </c>
       <c r="E140" t="n">
-        <v>331.1591315955093</v>
+        <v>331.7063314213004</v>
       </c>
       <c r="F140" t="n">
-        <v>11473600</v>
+        <v>12801000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>46036</v>
+        <v>46045</v>
       </c>
       <c r="B141" t="n">
-        <v>325.4287414550781</v>
+        <v>333.1488647460938</v>
       </c>
       <c r="C141" t="n">
-        <v>328.164607307781</v>
+        <v>335.4171450220839</v>
       </c>
       <c r="D141" t="n">
-        <v>323.1505332047328</v>
+        <v>329.6668536862397</v>
       </c>
       <c r="E141" t="n">
-        <v>328.164607307781</v>
+        <v>330.3632680425013</v>
       </c>
       <c r="F141" t="n">
-        <v>11210800</v>
+        <v>12904400</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>46037</v>
+        <v>46048</v>
       </c>
       <c r="B142" t="n">
-        <v>339.8840942382812</v>
+        <v>330.9999694824219</v>
       </c>
       <c r="C142" t="n">
-        <v>349.5242628055195</v>
+        <v>333.3777002269528</v>
       </c>
       <c r="D142" t="n">
-        <v>336.1832126341018</v>
+        <v>328.5327353128581</v>
       </c>
       <c r="E142" t="n">
-        <v>341.0480638104695</v>
+        <v>331.0795753102497</v>
       </c>
       <c r="F142" t="n">
-        <v>42188500</v>
+        <v>8646400</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>46038</v>
+        <v>46049</v>
       </c>
       <c r="B143" t="n">
-        <v>340.64013671875</v>
+        <v>336.6010131835938</v>
       </c>
       <c r="C143" t="n">
-        <v>348.0518575773862</v>
+        <v>339.4960601530208</v>
       </c>
       <c r="D143" t="n">
-        <v>339.7049656735853</v>
+        <v>332.8404426547893</v>
       </c>
       <c r="E143" t="n">
-        <v>344.7290280520938</v>
+        <v>334.7704739677407</v>
       </c>
       <c r="F143" t="n">
-        <v>18246100</v>
+        <v>11298100</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>46042</v>
+        <v>46050</v>
       </c>
       <c r="B144" t="n">
-        <v>325.4784851074219</v>
+        <v>340.5406799316406</v>
       </c>
       <c r="C144" t="n">
-        <v>340.3914306345235</v>
+        <v>343.7242451423734</v>
       </c>
       <c r="D144" t="n">
-        <v>325.2198117253413</v>
+        <v>336.9194041061418</v>
       </c>
       <c r="E144" t="n">
-        <v>339.0384352590497</v>
+        <v>341.2669389047847</v>
       </c>
       <c r="F144" t="n">
-        <v>22809900</v>
+        <v>12140100</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>46043</v>
+        <v>46051</v>
       </c>
       <c r="B145" t="n">
-        <v>324.44384765625</v>
+        <v>337.8048095703125</v>
       </c>
       <c r="C145" t="n">
-        <v>331.9252168077863</v>
+        <v>341.9732767406938</v>
       </c>
       <c r="D145" t="n">
-        <v>324.0061066799057</v>
+        <v>326.5131692249356</v>
       </c>
       <c r="E145" t="n">
-        <v>331.7162742776711</v>
+        <v>338.0535246503557</v>
       </c>
       <c r="F145" t="n">
-        <v>16789800</v>
+        <v>13844800</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>46044</v>
+        <v>46052</v>
       </c>
       <c r="B146" t="n">
-        <v>325.6874084472656</v>
+        <v>328.8610229492188</v>
       </c>
       <c r="C146" t="n">
-        <v>333.327928191825</v>
+        <v>338.1530146381896</v>
       </c>
       <c r="D146" t="n">
-        <v>325.2198228962958</v>
+        <v>327.4085353918609</v>
       </c>
       <c r="E146" t="n">
-        <v>331.7063314213004</v>
+        <v>333.6960598625758</v>
       </c>
       <c r="F146" t="n">
-        <v>12801000</v>
+        <v>12028100</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>46045</v>
+        <v>46055</v>
       </c>
       <c r="B147" t="n">
-        <v>333.1488647460938</v>
+        <v>339.6054992675781</v>
       </c>
       <c r="C147" t="n">
-        <v>335.4171450220839</v>
+        <v>342.4309292522656</v>
       </c>
       <c r="D147" t="n">
-        <v>329.6668536862397</v>
+        <v>327.4085325690498</v>
       </c>
       <c r="E147" t="n">
-        <v>330.3632680425013</v>
+        <v>329.0600043192495</v>
       </c>
       <c r="F147" t="n">
-        <v>12904400</v>
+        <v>12459100</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>46048</v>
+        <v>46056</v>
       </c>
       <c r="B148" t="n">
-        <v>330.9999694824219</v>
+        <v>334.0243225097656</v>
       </c>
       <c r="C148" t="n">
-        <v>333.3777002269528</v>
+        <v>345.2662309741439</v>
       </c>
       <c r="D148" t="n">
-        <v>328.5327353128581</v>
+        <v>328.3237624571021</v>
       </c>
       <c r="E148" t="n">
-        <v>331.0795753102497</v>
+        <v>343.2964271479137</v>
       </c>
       <c r="F148" t="n">
-        <v>8646400</v>
+        <v>12540000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>46049</v>
+        <v>46057</v>
       </c>
       <c r="B149" t="n">
-        <v>336.6010131835938</v>
+        <v>324.0657958984375</v>
       </c>
       <c r="C149" t="n">
-        <v>339.4960601530208</v>
+        <v>337.0586694483266</v>
       </c>
       <c r="D149" t="n">
-        <v>332.8404426547893</v>
+        <v>317.4300944641324</v>
       </c>
       <c r="E149" t="n">
-        <v>334.7704739677407</v>
+        <v>333.8751345918697</v>
       </c>
       <c r="F149" t="n">
-        <v>11298100</v>
+        <v>18176000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>46050</v>
+        <v>46058</v>
       </c>
       <c r="B150" t="n">
-        <v>340.5406799316406</v>
+        <v>329.0301513671875</v>
       </c>
       <c r="C150" t="n">
-        <v>343.7242451423734</v>
+        <v>332.8504111994827</v>
       </c>
       <c r="D150" t="n">
-        <v>336.9194041061418</v>
+        <v>318.0070824616777</v>
       </c>
       <c r="E150" t="n">
-        <v>341.2669389047847</v>
+        <v>321.1608029083129</v>
       </c>
       <c r="F150" t="n">
-        <v>12140100</v>
+        <v>14812000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>46051</v>
+        <v>46059</v>
       </c>
       <c r="B151" t="n">
-        <v>337.8048095703125</v>
+        <v>347.0570373535156</v>
       </c>
       <c r="C151" t="n">
-        <v>341.9732767406938</v>
+        <v>347.9225609957699</v>
       </c>
       <c r="D151" t="n">
-        <v>326.5131692249356</v>
+        <v>334.9197290027381</v>
       </c>
       <c r="E151" t="n">
-        <v>338.0535246503557</v>
+        <v>335.7653663679586</v>
       </c>
       <c r="F151" t="n">
-        <v>13844800</v>
+        <v>17025500</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>46052</v>
+        <v>46062</v>
       </c>
       <c r="B152" t="n">
-        <v>328.8610229492188</v>
+        <v>353.5832824707031</v>
       </c>
       <c r="C152" t="n">
-        <v>338.1530146381896</v>
+        <v>357.7517493161135</v>
       </c>
       <c r="D152" t="n">
-        <v>327.4085353918609</v>
+        <v>346.0123802368341</v>
       </c>
       <c r="E152" t="n">
-        <v>333.6960598625758</v>
+        <v>346.9674679294656</v>
       </c>
       <c r="F152" t="n">
-        <v>12028100</v>
+        <v>14594900</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>46055</v>
+        <v>46063</v>
       </c>
       <c r="B153" t="n">
-        <v>339.6054992675781</v>
+        <v>360.0498962402344</v>
       </c>
       <c r="C153" t="n">
-        <v>342.4309292522656</v>
+        <v>362.8852541785932</v>
       </c>
       <c r="D153" t="n">
-        <v>327.4085325690498</v>
+        <v>354.5582782923775</v>
       </c>
       <c r="E153" t="n">
-        <v>329.0600043192495</v>
+        <v>362.4574411737488</v>
       </c>
       <c r="F153" t="n">
-        <v>12459100</v>
+        <v>14622100</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>46056</v>
+        <v>46064</v>
       </c>
       <c r="B154" t="n">
-        <v>334.0243225097656</v>
+        <v>372.1672668457031</v>
       </c>
       <c r="C154" t="n">
-        <v>345.2662309741439</v>
+        <v>377.629039896409</v>
       </c>
       <c r="D154" t="n">
-        <v>328.3237624571021</v>
+        <v>366.4965816437437</v>
       </c>
       <c r="E154" t="n">
-        <v>343.2964271479137</v>
+        <v>368.177867532418</v>
       </c>
       <c r="F154" t="n">
-        <v>12540000</v>
+        <v>18651300</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>46057</v>
+        <v>46065</v>
       </c>
       <c r="B155" t="n">
-        <v>324.0657958984375</v>
+        <v>366.2080993652344</v>
       </c>
       <c r="C155" t="n">
-        <v>337.0586694483266</v>
+        <v>378.0469314082415</v>
       </c>
       <c r="D155" t="n">
-        <v>317.4300944641324</v>
+        <v>320.4445234579209</v>
       </c>
       <c r="E155" t="n">
-        <v>333.8751345918697</v>
+        <v>377.0520710624303</v>
       </c>
       <c r="F155" t="n">
-        <v>18176000</v>
+        <v>16835400</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>46058</v>
+        <v>46066</v>
       </c>
       <c r="B156" t="n">
-        <v>329.0301513671875</v>
+        <v>364.4770202636719</v>
       </c>
       <c r="C156" t="n">
-        <v>332.8504111994827</v>
+        <v>369.202606887416</v>
       </c>
       <c r="D156" t="n">
-        <v>318.0070824616777</v>
+        <v>358.9157545960688</v>
       </c>
       <c r="E156" t="n">
-        <v>321.1608029083129</v>
+        <v>367.2526891184118</v>
       </c>
       <c r="F156" t="n">
-        <v>14812000</v>
+        <v>10468200</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>46059</v>
+        <v>46070</v>
       </c>
       <c r="B157" t="n">
-        <v>347.0570373535156</v>
+        <v>362.328125</v>
       </c>
       <c r="C157" t="n">
-        <v>347.9225609957699</v>
+        <v>364.317845553848</v>
       </c>
       <c r="D157" t="n">
-        <v>334.9197290027381</v>
+        <v>354.4090153359624</v>
       </c>
       <c r="E157" t="n">
-        <v>335.7653663679586</v>
+        <v>360.0100835527605</v>
       </c>
       <c r="F157" t="n">
-        <v>17025500</v>
+        <v>10063800</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>46062</v>
+        <v>46071</v>
       </c>
       <c r="B158" t="n">
-        <v>353.5832824707031</v>
+        <v>360.3981018066406</v>
       </c>
       <c r="C158" t="n">
-        <v>357.7517493161135</v>
+        <v>367.4914605996805</v>
       </c>
       <c r="D158" t="n">
-        <v>346.0123802368341</v>
+        <v>358.8560501260037</v>
       </c>
       <c r="E158" t="n">
-        <v>346.9674679294656</v>
+        <v>361.9898539972341</v>
       </c>
       <c r="F158" t="n">
-        <v>14594900</v>
+        <v>7310500</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>46063</v>
+        <v>46072</v>
       </c>
       <c r="B159" t="n">
-        <v>360.0498962402344</v>
+        <v>358.5377197265625</v>
       </c>
       <c r="C159" t="n">
-        <v>362.8852541785932</v>
+        <v>360.9353063430657</v>
       </c>
       <c r="D159" t="n">
-        <v>354.5582782923775</v>
+        <v>355.6028696838767</v>
       </c>
       <c r="E159" t="n">
-        <v>362.4574411737488</v>
+        <v>357.8711499638003</v>
       </c>
       <c r="F159" t="n">
-        <v>14622100</v>
+        <v>6346500</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>46064</v>
+        <v>46073</v>
       </c>
       <c r="B160" t="n">
-        <v>372.1672668457031</v>
+        <v>368.6355590820312</v>
       </c>
       <c r="C160" t="n">
-        <v>377.629039896409</v>
+        <v>370.2870308906031</v>
       </c>
       <c r="D160" t="n">
-        <v>366.4965816437437</v>
+        <v>357.2543543574776</v>
       </c>
       <c r="E160" t="n">
-        <v>368.177867532418</v>
+        <v>357.9308521024652</v>
       </c>
       <c r="F160" t="n">
-        <v>18651300</v>
+        <v>9009200</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>46065</v>
+        <v>46076</v>
       </c>
       <c r="B161" t="n">
-        <v>366.2080993652344</v>
+        <v>368.1380920410156</v>
       </c>
       <c r="C161" t="n">
-        <v>378.0469314082415</v>
+        <v>371.5106524700655</v>
       </c>
       <c r="D161" t="n">
-        <v>320.4445234579209</v>
+        <v>364.576475376613</v>
       </c>
       <c r="E161" t="n">
-        <v>377.0520710624303</v>
+        <v>365.1236667255391</v>
       </c>
       <c r="F161" t="n">
-        <v>16835400</v>
+        <v>9550200</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>46066</v>
+        <v>46077</v>
       </c>
       <c r="B162" t="n">
-        <v>364.4770202636719</v>
+        <v>383.7673645019531</v>
       </c>
       <c r="C162" t="n">
-        <v>369.202606887416</v>
+        <v>387.1797280779624</v>
       </c>
       <c r="D162" t="n">
-        <v>358.9157545960688</v>
+        <v>374.1172073526877</v>
       </c>
       <c r="E162" t="n">
-        <v>367.2526891184118</v>
+        <v>377.4499954626336</v>
       </c>
       <c r="F162" t="n">
-        <v>10468200</v>
+        <v>13269500</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>46070</v>
+        <v>46078</v>
       </c>
       <c r="B163" t="n">
-        <v>362.328125</v>
+        <v>385.7371826171875</v>
       </c>
       <c r="C163" t="n">
-        <v>364.317845553848</v>
+        <v>388.2044166508074</v>
       </c>
       <c r="D163" t="n">
-        <v>354.4090153359624</v>
+        <v>382.8520635515886</v>
       </c>
       <c r="E163" t="n">
-        <v>360.0100835527605</v>
+        <v>388.2044166508074</v>
       </c>
       <c r="F163" t="n">
-        <v>10063800</v>
+        <v>10948400</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>46071</v>
+        <v>46079</v>
       </c>
       <c r="B164" t="n">
-        <v>360.3981018066406</v>
+        <v>374.8733215332031</v>
       </c>
       <c r="C164" t="n">
-        <v>367.4914605996805</v>
+        <v>384.4836760415777</v>
       </c>
       <c r="D164" t="n">
-        <v>358.8560501260037</v>
+        <v>367.7998791031673</v>
       </c>
       <c r="E164" t="n">
-        <v>361.9898539972341</v>
+        <v>384.1951580425536</v>
       </c>
       <c r="F164" t="n">
-        <v>7310500</v>
+        <v>14535700</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>46072</v>
+        <v>46080</v>
       </c>
       <c r="B165" t="n">
-        <v>358.5377197265625</v>
+        <v>372.6547546386719</v>
       </c>
       <c r="C165" t="n">
-        <v>360.9353063430657</v>
+        <v>374.7439673230082</v>
       </c>
       <c r="D165" t="n">
-        <v>355.6028696838767</v>
+        <v>366.7253958022188</v>
       </c>
       <c r="E165" t="n">
-        <v>357.8711499638003</v>
+        <v>368.2376028761936</v>
       </c>
       <c r="F165" t="n">
-        <v>6346500</v>
+        <v>9186600</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>46073</v>
+        <v>46083</v>
       </c>
       <c r="B166" t="n">
-        <v>368.6355590820312</v>
+        <v>367.2128601074219</v>
       </c>
       <c r="C166" t="n">
-        <v>370.2870308906031</v>
+        <v>371.1823732345651</v>
       </c>
       <c r="D166" t="n">
-        <v>357.2543543574776</v>
+        <v>362.7757917991398</v>
       </c>
       <c r="E166" t="n">
-        <v>357.9308521024652</v>
+        <v>363.482134090646</v>
       </c>
       <c r="F166" t="n">
-        <v>9009200</v>
+        <v>12571600</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>46076</v>
+        <v>46084</v>
       </c>
       <c r="B167" t="n">
-        <v>368.1380920410156</v>
+        <v>351.3150329589844</v>
       </c>
       <c r="C167" t="n">
-        <v>371.5106524700655</v>
+        <v>354.1503909697605</v>
       </c>
       <c r="D167" t="n">
-        <v>364.576475376613</v>
+        <v>342.3712483136142</v>
       </c>
       <c r="E167" t="n">
-        <v>365.1236667255391</v>
+        <v>347.753415977925</v>
       </c>
       <c r="F167" t="n">
-        <v>9550200</v>
+        <v>18580200</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>46077</v>
+        <v>46085</v>
       </c>
       <c r="B168" t="n">
-        <v>383.7673645019531</v>
+        <v>355.6028747558594</v>
       </c>
       <c r="C168" t="n">
-        <v>387.1797280779624</v>
+        <v>359.2341088470799</v>
       </c>
       <c r="D168" t="n">
-        <v>374.1172073526877</v>
+        <v>352.7277138615793</v>
       </c>
       <c r="E168" t="n">
-        <v>377.4499954626336</v>
+        <v>355.5929164372393</v>
       </c>
       <c r="F168" t="n">
-        <v>13269500</v>
+        <v>12131100</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>46078</v>
+        <v>46086</v>
       </c>
       <c r="B169" t="n">
-        <v>385.7371826171875</v>
+        <v>352.041259765625</v>
       </c>
       <c r="C169" t="n">
-        <v>388.2044166508074</v>
+        <v>357.6224419722406</v>
       </c>
       <c r="D169" t="n">
-        <v>382.8520635515886</v>
+        <v>342.0329673325376</v>
       </c>
       <c r="E169" t="n">
-        <v>388.2044166508074</v>
+        <v>353.0759230038478</v>
       </c>
       <c r="F169" t="n">
-        <v>10948400</v>
+        <v>16249800</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>46079</v>
+        <v>46087</v>
       </c>
       <c r="B170" t="n">
-        <v>374.8733215332031</v>
+        <v>337.1482238769531</v>
       </c>
       <c r="C170" t="n">
-        <v>384.4836760415777</v>
+        <v>346.927687332115</v>
       </c>
       <c r="D170" t="n">
-        <v>367.7998791031673</v>
+        <v>334.9595190581414</v>
       </c>
       <c r="E170" t="n">
-        <v>384.1951580425536</v>
+        <v>341.7345153172319</v>
       </c>
       <c r="F170" t="n">
-        <v>14535700</v>
+        <v>13803000</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>46080</v>
+        <v>46090</v>
       </c>
       <c r="B171" t="n">
-        <v>372.6547546386719</v>
+        <v>346.9078063964844</v>
       </c>
       <c r="C171" t="n">
-        <v>374.7439673230082</v>
+        <v>347.6041904053892</v>
       </c>
       <c r="D171" t="n">
-        <v>366.7253958022188</v>
+        <v>330.214051409159</v>
       </c>
       <c r="E171" t="n">
-        <v>368.2376028761936</v>
+        <v>333.8751301072361</v>
       </c>
       <c r="F171" t="n">
-        <v>9186600</v>
+        <v>19182800</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="B172" t="n">
-        <v>367.2128601074219</v>
+        <v>345.3060607910156</v>
       </c>
       <c r="C172" t="n">
-        <v>371.1823732345651</v>
+        <v>351.6831190109945</v>
       </c>
       <c r="D172" t="n">
-        <v>362.7757917991398</v>
+        <v>342.5403503481588</v>
       </c>
       <c r="E172" t="n">
-        <v>363.482134090646</v>
+        <v>346.6789728742912</v>
       </c>
       <c r="F172" t="n">
-        <v>12571600</v>
+        <v>12985600</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>46084</v>
+        <v>46092</v>
       </c>
       <c r="B173" t="n">
-        <v>351.3150329589844</v>
+        <v>352.7376403808594</v>
       </c>
       <c r="C173" t="n">
-        <v>354.1503909697605</v>
+        <v>355.5133089208941</v>
       </c>
       <c r="D173" t="n">
-        <v>342.3712483136142</v>
+        <v>348.5592152745862</v>
       </c>
       <c r="E173" t="n">
-        <v>347.753415977925</v>
+        <v>352.1108735788459</v>
       </c>
       <c r="F173" t="n">
-        <v>18580200</v>
+        <v>10683300</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>46085</v>
+        <v>46093</v>
       </c>
       <c r="B174" t="n">
-        <v>355.6028747558594</v>
+        <v>334.9794006347656</v>
       </c>
       <c r="C174" t="n">
-        <v>359.2341088470799</v>
+        <v>345.107101488022</v>
       </c>
       <c r="D174" t="n">
-        <v>352.7277138615793</v>
+        <v>334.6511100969132</v>
       </c>
       <c r="E174" t="n">
-        <v>355.5929164372393</v>
+        <v>344.1520137473617</v>
       </c>
       <c r="F174" t="n">
-        <v>12131100</v>
+        <v>17549400</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>46086</v>
+        <v>46094</v>
       </c>
       <c r="B175" t="n">
-        <v>352.041259765625</v>
+        <v>336.5711669921875</v>
       </c>
       <c r="C175" t="n">
-        <v>357.6224419722406</v>
+        <v>342.749240611443</v>
       </c>
       <c r="D175" t="n">
-        <v>342.0329673325376</v>
+        <v>334.4919127238255</v>
       </c>
       <c r="E175" t="n">
-        <v>353.0759230038478</v>
+        <v>342.1523487531383</v>
       </c>
       <c r="F175" t="n">
-        <v>16249800</v>
+        <v>17299900</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>46087</v>
+        <v>46097</v>
       </c>
       <c r="B176" t="n">
-        <v>337.1482238769531</v>
+        <v>338.4813232421875</v>
       </c>
       <c r="C176" t="n">
-        <v>346.927687332115</v>
+        <v>342.8587023923161</v>
       </c>
       <c r="D176" t="n">
-        <v>334.9595190581414</v>
+        <v>338.0734268850067</v>
       </c>
       <c r="E176" t="n">
-        <v>341.7345153172319</v>
+        <v>339.4960697956714</v>
       </c>
       <c r="F176" t="n">
-        <v>13803000</v>
+        <v>11123500</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>46090</v>
+        <v>46098</v>
       </c>
       <c r="B177" t="n">
-        <v>346.9078063964844</v>
+        <v>345.1716613769531</v>
       </c>
       <c r="C177" t="n">
-        <v>347.6041904053892</v>
+        <v>345.9498377627922</v>
       </c>
       <c r="D177" t="n">
-        <v>330.214051409159</v>
+        <v>337.6093542809213</v>
       </c>
       <c r="E177" t="n">
-        <v>333.8751301072361</v>
+        <v>339.8042263672759</v>
       </c>
       <c r="F177" t="n">
-        <v>19182800</v>
+        <v>11434600</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>46091</v>
+        <v>46099</v>
       </c>
       <c r="B178" t="n">
-        <v>345.3060607910156</v>
+        <v>338.7766418457031</v>
       </c>
       <c r="C178" t="n">
-        <v>351.6831190109945</v>
+        <v>347.1370678303785</v>
       </c>
       <c r="D178" t="n">
-        <v>342.5403503481588</v>
+        <v>338.5471682530561</v>
       </c>
       <c r="E178" t="n">
-        <v>346.6789728742912</v>
+        <v>344.9721243843986</v>
       </c>
       <c r="F178" t="n">
-        <v>12985600</v>
+        <v>12632600</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>46092</v>
+        <v>46100</v>
       </c>
       <c r="B179" t="n">
-        <v>352.7376403808594</v>
+        <v>337.9984741210938</v>
       </c>
       <c r="C179" t="n">
-        <v>355.5133089208941</v>
+        <v>339.1058661505584</v>
       </c>
       <c r="D179" t="n">
-        <v>348.5592152745862</v>
+        <v>324.4302424876738</v>
       </c>
       <c r="E179" t="n">
-        <v>352.1108735788459</v>
+        <v>328.4508257509243</v>
       </c>
       <c r="F179" t="n">
-        <v>10683300</v>
+        <v>15411600</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>46093</v>
+        <v>46101</v>
       </c>
       <c r="B180" t="n">
-        <v>334.9794006347656</v>
+        <v>328.4707641601562</v>
       </c>
       <c r="C180" t="n">
-        <v>345.107101488022</v>
+        <v>336.8112479482066</v>
       </c>
       <c r="D180" t="n">
-        <v>334.6511100969132</v>
+        <v>325.1385712858396</v>
       </c>
       <c r="E180" t="n">
-        <v>344.1520137473617</v>
+        <v>335.8933840112334</v>
       </c>
       <c r="F180" t="n">
-        <v>17549400</v>
+        <v>17424200</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>46094</v>
+        <v>46104</v>
       </c>
       <c r="B181" t="n">
-        <v>336.5711669921875</v>
+        <v>337.6592712402344</v>
       </c>
       <c r="C181" t="n">
-        <v>342.749240611443</v>
+        <v>342.6076743711966</v>
       </c>
       <c r="D181" t="n">
-        <v>334.4919127238255</v>
+        <v>330.3264373947262</v>
       </c>
       <c r="E181" t="n">
-        <v>342.1523487531383</v>
+        <v>330.3264373947262</v>
       </c>
       <c r="F181" t="n">
-        <v>17299900</v>
+        <v>15857200</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>46097</v>
+        <v>46105</v>
       </c>
       <c r="B182" t="n">
-        <v>338.4813232421875</v>
+        <v>342.4480285644531</v>
       </c>
       <c r="C182" t="n">
-        <v>342.8587023923161</v>
+        <v>344.0742250937163</v>
       </c>
       <c r="D182" t="n">
-        <v>338.0734268850067</v>
+        <v>333.2395826332184</v>
       </c>
       <c r="E182" t="n">
-        <v>339.4960697956714</v>
+        <v>334.785979471341</v>
       </c>
       <c r="F182" t="n">
-        <v>11123500</v>
+        <v>9725000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>46098</v>
+        <v>46106</v>
       </c>
       <c r="B183" t="n">
-        <v>345.1716613769531</v>
+        <v>346.9375305175781</v>
       </c>
       <c r="C183" t="n">
-        <v>345.9498377627922</v>
+        <v>349.6312345218189</v>
       </c>
       <c r="D183" t="n">
-        <v>337.6093542809213</v>
+        <v>342.6974600511519</v>
       </c>
       <c r="E183" t="n">
-        <v>339.8042263672759</v>
+        <v>345.1916191490497</v>
       </c>
       <c r="F183" t="n">
-        <v>11434600</v>
+        <v>12166900</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>46099</v>
+        <v>46107</v>
       </c>
       <c r="B184" t="n">
-        <v>338.7766418457031</v>
+        <v>325.3480529785156</v>
       </c>
       <c r="C184" t="n">
-        <v>347.1370678303785</v>
+        <v>340.1134921176816</v>
       </c>
       <c r="D184" t="n">
-        <v>338.5471682530561</v>
+        <v>324.6097916777539</v>
       </c>
       <c r="E184" t="n">
-        <v>344.9721243843986</v>
+        <v>339.0260424773275</v>
       </c>
       <c r="F184" t="n">
-        <v>12632600</v>
+        <v>14560200</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>46100</v>
+        <v>46108</v>
       </c>
       <c r="B185" t="n">
-        <v>337.9984741210938</v>
+        <v>325.9765930175781</v>
       </c>
       <c r="C185" t="n">
-        <v>339.1058661505584</v>
+        <v>328.790011660255</v>
       </c>
       <c r="D185" t="n">
-        <v>324.4302424876738</v>
+        <v>321.5569506024941</v>
       </c>
       <c r="E185" t="n">
-        <v>328.4508257509243</v>
+        <v>324.0710518991527</v>
       </c>
       <c r="F185" t="n">
-        <v>15411600</v>
+        <v>14484500</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>46101</v>
+        <v>46111</v>
       </c>
       <c r="B186" t="n">
-        <v>328.4707641601562</v>
+        <v>315.7605285644531</v>
       </c>
       <c r="C186" t="n">
-        <v>336.8112479482066</v>
+        <v>328.8299277791251</v>
       </c>
       <c r="D186" t="n">
-        <v>325.1385712858396</v>
+        <v>313.0668246730703</v>
       </c>
       <c r="E186" t="n">
-        <v>335.8933840112334</v>
+        <v>326.4355412347163</v>
       </c>
       <c r="F186" t="n">
-        <v>17424200</v>
+        <v>15740000</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>46104</v>
+        <v>46112</v>
       </c>
       <c r="B187" t="n">
-        <v>337.6592712402344</v>
+        <v>337.1604309082031</v>
       </c>
       <c r="C187" t="n">
-        <v>342.6076743711966</v>
+        <v>337.6193476462005</v>
       </c>
       <c r="D187" t="n">
-        <v>330.3264373947262</v>
+        <v>320.3897079737437</v>
       </c>
       <c r="E187" t="n">
-        <v>330.3264373947262</v>
+        <v>321.5569573535184</v>
       </c>
       <c r="F187" t="n">
-        <v>15857200</v>
+        <v>18488000</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>46105</v>
+        <v>46113</v>
       </c>
       <c r="B188" t="n">
-        <v>342.4480285644531</v>
+        <v>340.692138671875</v>
       </c>
       <c r="C188" t="n">
-        <v>344.0742250937163</v>
+        <v>347.8653425105511</v>
       </c>
       <c r="D188" t="n">
-        <v>333.2395826332184</v>
+        <v>338.9562137218917</v>
       </c>
       <c r="E188" t="n">
-        <v>334.785979471341</v>
+        <v>343.0965116413069</v>
       </c>
       <c r="F188" t="n">
-        <v>9725000</v>
+        <v>15011600</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="B189" t="n">
-        <v>346.9375305175781</v>
+        <v>338.2478942871094</v>
       </c>
       <c r="C189" t="n">
-        <v>349.6312345218189</v>
+        <v>341.270813945436</v>
       </c>
       <c r="D189" t="n">
-        <v>342.6974600511519</v>
+        <v>326.0364704402683</v>
       </c>
       <c r="E189" t="n">
-        <v>345.1916191490497</v>
+        <v>326.0763855114465</v>
       </c>
       <c r="F189" t="n">
-        <v>12166900</v>
+        <v>8994600</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>46107</v>
+        <v>46118</v>
       </c>
       <c r="B190" t="n">
-        <v>325.3480529785156</v>
+        <v>340.9615173339844</v>
       </c>
       <c r="C190" t="n">
-        <v>340.1134921176816</v>
+        <v>343.3958189226665</v>
       </c>
       <c r="D190" t="n">
-        <v>324.6097916777539</v>
+        <v>337.8288390556908</v>
       </c>
       <c r="E190" t="n">
-        <v>339.0260424773275</v>
+        <v>338.9562037807292</v>
       </c>
       <c r="F190" t="n">
-        <v>14560200</v>
+        <v>5884800</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>46108</v>
+        <v>46119</v>
       </c>
       <c r="B191" t="n">
-        <v>325.9765930175781</v>
+        <v>344.5132141113281</v>
       </c>
       <c r="C191" t="n">
-        <v>328.790011660255</v>
+        <v>344.7227149499429</v>
       </c>
       <c r="D191" t="n">
-        <v>321.5569506024941</v>
+        <v>334.8657933542661</v>
       </c>
       <c r="E191" t="n">
-        <v>324.0710518991527</v>
+        <v>338.6469470598911</v>
       </c>
       <c r="F191" t="n">
-        <v>14484500</v>
+        <v>6823500</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>46111</v>
+        <v>46120</v>
       </c>
       <c r="B192" t="n">
-        <v>315.7605285644531</v>
+        <v>365.0451049804688</v>
       </c>
       <c r="C192" t="n">
-        <v>328.8299277791251</v>
+        <v>373.4254731273044</v>
       </c>
       <c r="D192" t="n">
-        <v>313.0668246730703</v>
+        <v>358.4006617540148</v>
       </c>
       <c r="E192" t="n">
-        <v>326.4355412347163</v>
+        <v>369.4248627966387</v>
       </c>
       <c r="F192" t="n">
-        <v>15740000</v>
+        <v>16356900</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>46112</v>
+        <v>46121</v>
       </c>
       <c r="B193" t="n">
-        <v>337.1604309082031</v>
+        <v>364.6360778808594</v>
       </c>
       <c r="C193" t="n">
-        <v>337.6193476462005</v>
+        <v>367.3098396033888</v>
       </c>
       <c r="D193" t="n">
-        <v>320.3897079737437</v>
+        <v>359.877233228603</v>
       </c>
       <c r="E193" t="n">
-        <v>321.5569573535184</v>
+        <v>362.4511920505476</v>
       </c>
       <c r="F193" t="n">
-        <v>18488000</v>
+        <v>9246000</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="B194" t="n">
-        <v>340.692138671875</v>
+        <v>369.734130859375</v>
       </c>
       <c r="C194" t="n">
-        <v>347.8653425105511</v>
+        <v>377.1168353024966</v>
       </c>
       <c r="D194" t="n">
-        <v>338.9562137218917</v>
+        <v>368.8861107224818</v>
       </c>
       <c r="E194" t="n">
-        <v>343.0965116413069</v>
+        <v>374.7124624079937</v>
       </c>
       <c r="F194" t="n">
-        <v>15011600</v>
+        <v>13168200</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>46114</v>
+        <v>46125</v>
       </c>
       <c r="B195" t="n">
-        <v>338.2478942871094</v>
+        <v>368.70654296875</v>
       </c>
       <c r="C195" t="n">
-        <v>341.270813945436</v>
+        <v>370.5921113356213</v>
       </c>
       <c r="D195" t="n">
-        <v>326.0364704402683</v>
+        <v>365.1947476205656</v>
       </c>
       <c r="E195" t="n">
-        <v>326.0763855114465</v>
+        <v>369.3949332866031</v>
       </c>
       <c r="F195" t="n">
-        <v>8994600</v>
+        <v>9596300</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>46118</v>
+        <v>46126</v>
       </c>
       <c r="B196" t="n">
-        <v>340.9615173339844</v>
+        <v>379.00244140625</v>
       </c>
       <c r="C196" t="n">
-        <v>343.3958189226665</v>
+        <v>381.2671268282746</v>
       </c>
       <c r="D196" t="n">
-        <v>337.8288390556908</v>
+        <v>372.3480117664943</v>
       </c>
       <c r="E196" t="n">
-        <v>338.9562037807292</v>
+        <v>378.1544212529939</v>
       </c>
       <c r="F196" t="n">
-        <v>5884800</v>
+        <v>12859500</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>46119</v>
+        <v>46127</v>
       </c>
       <c r="B197" t="n">
-        <v>344.5132141113281</v>
+        <v>374.2236328125</v>
       </c>
       <c r="C197" t="n">
-        <v>344.7227149499429</v>
+        <v>381.0875634419847</v>
       </c>
       <c r="D197" t="n">
-        <v>334.8657933542661</v>
+        <v>371.3403703144419</v>
       </c>
       <c r="E197" t="n">
-        <v>338.6469470598911</v>
+        <v>380.5188878671302</v>
       </c>
       <c r="F197" t="n">
-        <v>6823500</v>
+        <v>14955500</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>46120</v>
+        <v>46128</v>
       </c>
       <c r="B198" t="n">
-        <v>365.0451049804688</v>
+        <v>362.5010681152344</v>
       </c>
       <c r="C198" t="n">
-        <v>373.4254731273044</v>
+        <v>369.3350697318818</v>
       </c>
       <c r="D198" t="n">
-        <v>358.4006617540148</v>
+        <v>359.7075918216732</v>
       </c>
       <c r="E198" t="n">
-        <v>369.4248627966387</v>
+        <v>367.9981737410995</v>
       </c>
       <c r="F198" t="n">
-        <v>16356900</v>
+        <v>26405800</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>46121</v>
+        <v>46129</v>
       </c>
       <c r="B199" t="n">
-        <v>364.6360778808594</v>
+        <v>369.6343688964844</v>
       </c>
       <c r="C199" t="n">
-        <v>367.3098396033888</v>
+        <v>374.7024866580013</v>
       </c>
       <c r="D199" t="n">
-        <v>359.877233228603</v>
+        <v>364.286906540967</v>
       </c>
       <c r="E199" t="n">
-        <v>362.4511920505476</v>
+        <v>372.3280728321357</v>
       </c>
       <c r="F199" t="n">
-        <v>9246000</v>
+        <v>18419400</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>46122</v>
+        <v>46132</v>
       </c>
       <c r="B200" t="n">
-        <v>369.734130859375</v>
+        <v>365.3843078613281</v>
       </c>
       <c r="C200" t="n">
-        <v>377.1168353024966</v>
+        <v>369.2053765069833</v>
       </c>
       <c r="D200" t="n">
-        <v>368.8861107224818</v>
+        <v>363.3989670361152</v>
       </c>
       <c r="E200" t="n">
-        <v>374.7124624079937</v>
+        <v>368.3573563560101</v>
       </c>
       <c r="F200" t="n">
-        <v>13168200</v>
+        <v>11638300</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>46125</v>
+        <v>46133</v>
       </c>
       <c r="B201" t="n">
-        <v>368.70654296875</v>
+        <v>367.2200012207031</v>
       </c>
       <c r="C201" t="n">
-        <v>370.5921113356213</v>
+        <v>369.8837764053379</v>
       </c>
       <c r="D201" t="n">
-        <v>365.1947476205656</v>
+        <v>364.2569391372449</v>
       </c>
       <c r="E201" t="n">
-        <v>369.3949332866031</v>
+        <v>367.2200012207031</v>
       </c>
       <c r="F201" t="n">
-        <v>9596300</v>
+        <v>9808200</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>46126</v>
+        <v>46134</v>
       </c>
       <c r="B202" t="n">
-        <v>379.00244140625</v>
+        <v>386.5347900390625</v>
       </c>
       <c r="C202" t="n">
-        <v>381.2671268282746</v>
+        <v>387.0036931518485</v>
       </c>
       <c r="D202" t="n">
-        <v>372.3480117664943</v>
+        <v>369.7740536326661</v>
       </c>
       <c r="E202" t="n">
-        <v>378.1544212529939</v>
+        <v>370.9113743117207</v>
       </c>
       <c r="F202" t="n">
-        <v>12859500</v>
+        <v>16317200</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>46127</v>
+        <v>46135</v>
       </c>
       <c r="B203" t="n">
-        <v>374.2236328125</v>
+        <v>381.7659606933594</v>
       </c>
       <c r="C203" t="n">
-        <v>381.0875634419847</v>
+        <v>387.8517148042079</v>
       </c>
       <c r="D203" t="n">
-        <v>371.3403703144419</v>
+        <v>374.9319588749379</v>
       </c>
       <c r="E203" t="n">
-        <v>380.5188878671302</v>
+        <v>383.3522421798608</v>
       </c>
       <c r="F203" t="n">
-        <v>14955500</v>
+        <v>12224900</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>46128</v>
+        <v>46136</v>
       </c>
       <c r="B204" t="n">
-        <v>362.5010681152344</v>
+        <v>401.5196838378906</v>
       </c>
       <c r="C204" t="n">
-        <v>369.3350697318818</v>
+        <v>408.5332577264124</v>
       </c>
       <c r="D204" t="n">
-        <v>359.7075918216732</v>
+        <v>392.9298148580963</v>
       </c>
       <c r="E204" t="n">
-        <v>367.9981737410995</v>
+        <v>395.2144730265238</v>
       </c>
       <c r="F204" t="n">
-        <v>26405800</v>
+        <v>21603600</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>46129</v>
+        <v>46139</v>
       </c>
       <c r="B205" t="n">
-        <v>369.6343688964844</v>
+        <v>404.0338134765625</v>
       </c>
       <c r="C205" t="n">
-        <v>374.7024866580013</v>
+        <v>413.5315599359024</v>
       </c>
       <c r="D205" t="n">
-        <v>364.286906540967</v>
+        <v>399.4644971636646</v>
       </c>
       <c r="E205" t="n">
-        <v>372.3280728321357</v>
+        <v>412.7833122399991</v>
       </c>
       <c r="F205" t="n">
-        <v>18419400</v>
+        <v>16561200</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>46132</v>
+        <v>46140</v>
       </c>
       <c r="B206" t="n">
-        <v>365.3843078613281</v>
+        <v>391.42333984375</v>
       </c>
       <c r="C206" t="n">
-        <v>369.2053765069833</v>
+        <v>396.9404184279585</v>
       </c>
       <c r="D206" t="n">
-        <v>363.3989670361152</v>
+        <v>383.8012056418656</v>
       </c>
       <c r="E206" t="n">
-        <v>368.3573563560101</v>
+        <v>391.2038526301569</v>
       </c>
       <c r="F206" t="n">
-        <v>11638300</v>
+        <v>14715800</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>46133</v>
+        <v>46141</v>
       </c>
       <c r="B207" t="n">
-        <v>367.2200012207031</v>
+        <v>392.9098510742188</v>
       </c>
       <c r="C207" t="n">
-        <v>369.8837764053379</v>
+        <v>394.9251510773962</v>
       </c>
       <c r="D207" t="n">
-        <v>364.2569391372449</v>
+        <v>387.2730576960421</v>
       </c>
       <c r="E207" t="n">
-        <v>367.2200012207031</v>
+        <v>391.9920175913842</v>
       </c>
       <c r="F207" t="n">
-        <v>9808200</v>
+        <v>10313000</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>46134</v>
+        <v>46142</v>
       </c>
       <c r="B208" t="n">
-        <v>386.5347900390625</v>
+        <v>395.1346435546875</v>
       </c>
       <c r="C208" t="n">
-        <v>387.0036931518485</v>
+        <v>397.8582761473064</v>
       </c>
       <c r="D208" t="n">
-        <v>369.7740536326661</v>
+        <v>384.808819190422</v>
       </c>
       <c r="E208" t="n">
-        <v>370.9113743117207</v>
+        <v>396.8805548572255</v>
       </c>
       <c r="F208" t="n">
-        <v>16317200</v>
+        <v>12788100</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>46135</v>
+        <v>46143</v>
       </c>
       <c r="B209" t="n">
-        <v>381.7659606933594</v>
+        <v>396.7409057617188</v>
       </c>
       <c r="C209" t="n">
-        <v>387.8517148042079</v>
+        <v>403.0461167104827</v>
       </c>
       <c r="D209" t="n">
-        <v>374.9319588749379</v>
+        <v>391.213840773603</v>
       </c>
       <c r="E209" t="n">
-        <v>383.3522421798608</v>
+        <v>392.5207776820772</v>
       </c>
       <c r="F209" t="n">
-        <v>12224900</v>
+        <v>9926400</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>46136</v>
+        <v>46146</v>
       </c>
       <c r="B210" t="n">
-        <v>401.5196838378906</v>
+        <v>400.6716613769531</v>
       </c>
       <c r="C210" t="n">
-        <v>408.5332577264124</v>
+        <v>406.7474594572097</v>
       </c>
       <c r="D210" t="n">
-        <v>392.9298148580963</v>
+        <v>394.2766645320596</v>
       </c>
       <c r="E210" t="n">
-        <v>395.2144730265238</v>
+        <v>403.5748660890813</v>
       </c>
       <c r="F210" t="n">
-        <v>21603600</v>
+        <v>9978500</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>46139</v>
+        <v>46147</v>
       </c>
       <c r="B211" t="n">
-        <v>404.0338134765625</v>
+        <v>393.488525390625</v>
       </c>
       <c r="C211" t="n">
-        <v>413.5315599359024</v>
+        <v>405.1811446322546</v>
       </c>
       <c r="D211" t="n">
-        <v>399.4644971636646</v>
+        <v>391.6827566127574</v>
       </c>
       <c r="E211" t="n">
-        <v>412.7833122399991</v>
+        <v>403.6547204596296</v>
       </c>
       <c r="F211" t="n">
-        <v>16561200</v>
+        <v>14579000</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="B212" t="n">
-        <v>391.42333984375</v>
+        <v>418.5198974609375</v>
       </c>
       <c r="C212" t="n">
-        <v>396.9404184279585</v>
+        <v>418.719442367678</v>
       </c>
       <c r="D212" t="n">
-        <v>383.8012056418656</v>
+        <v>399.7139317360712</v>
       </c>
       <c r="E212" t="n">
-        <v>391.2038526301569</v>
+        <v>401.4598431080775</v>
       </c>
       <c r="F212" t="n">
-        <v>14715800</v>
+        <v>17736400</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>46141</v>
+        <v>46149</v>
       </c>
       <c r="B213" t="n">
-        <v>392.9098510742188</v>
+        <v>413.182373046875</v>
       </c>
       <c r="C213" t="n">
-        <v>394.9251510773962</v>
+        <v>419.0187111847754</v>
       </c>
       <c r="D213" t="n">
-        <v>387.2730576960421</v>
+        <v>407.1564763896412</v>
       </c>
       <c r="E213" t="n">
-        <v>391.9920175913842</v>
+        <v>417.1131700589296</v>
       </c>
       <c r="F213" t="n">
-        <v>10313000</v>
+        <v>13403200</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>46142</v>
+        <v>46150</v>
       </c>
       <c r="B214" t="n">
-        <v>395.1346435546875</v>
+        <v>410.7181396484375</v>
       </c>
       <c r="C214" t="n">
-        <v>397.8582761473064</v>
+        <v>416.025717257243</v>
       </c>
       <c r="D214" t="n">
-        <v>384.808819190422</v>
+        <v>399.9433850490627</v>
       </c>
       <c r="E214" t="n">
-        <v>396.8805548572255</v>
+        <v>415.9758462562264</v>
       </c>
       <c r="F214" t="n">
-        <v>12788100</v>
+        <v>18531200</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>46143</v>
+        <v>46153</v>
       </c>
       <c r="B215" t="n">
-        <v>396.7409057617188</v>
+        <v>403.5948486328125</v>
       </c>
       <c r="C215" t="n">
-        <v>403.0461167104827</v>
+        <v>406.7773980105824</v>
       </c>
       <c r="D215" t="n">
-        <v>391.213840773603</v>
+        <v>397.2596785679677</v>
       </c>
       <c r="E215" t="n">
-        <v>392.5207776820772</v>
+        <v>405.7896903250927</v>
       </c>
       <c r="F215" t="n">
-        <v>9926400</v>
+        <v>14680000</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="B216" t="n">
-        <v>400.6716613769531</v>
+        <v>396.351806640625</v>
       </c>
       <c r="C216" t="n">
-        <v>406.7474594572097</v>
+        <v>401.3002097321041</v>
       </c>
       <c r="D216" t="n">
-        <v>394.2766645320596</v>
+        <v>385.2178768500887</v>
       </c>
       <c r="E216" t="n">
-        <v>403.5748660890813</v>
+        <v>396.8207097656788</v>
       </c>
       <c r="F216" t="n">
-        <v>9978500</v>
+        <v>18121800</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>46147</v>
+        <v>46155</v>
       </c>
       <c r="B217" t="n">
-        <v>393.488525390625</v>
+        <v>398.8659057617188</v>
       </c>
       <c r="C217" t="n">
-        <v>405.1811446322546</v>
+        <v>403.734509131243</v>
       </c>
       <c r="D217" t="n">
-        <v>391.6827566127574</v>
+        <v>390.5553811479706</v>
       </c>
       <c r="E217" t="n">
-        <v>403.6547204596296</v>
+        <v>397.3394816307741</v>
       </c>
       <c r="F217" t="n">
-        <v>14579000</v>
+        <v>13127800</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>46148</v>
+        <v>46156</v>
       </c>
       <c r="B218" t="n">
-        <v>418.5198974609375</v>
+        <v>416.7440490722656</v>
       </c>
       <c r="C218" t="n">
-        <v>418.719442367678</v>
+        <v>420.9841194624343</v>
       </c>
       <c r="D218" t="n">
-        <v>399.7139317360712</v>
+        <v>401.1605481802736</v>
       </c>
       <c r="E218" t="n">
-        <v>401.4598431080775</v>
+        <v>402.2679401856103</v>
       </c>
       <c r="F218" t="n">
-        <v>17736400</v>
+        <v>18577100</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>46149</v>
+        <v>46157</v>
       </c>
       <c r="B219" t="n">
-        <v>413.182373046875</v>
+        <v>403.4053039550781</v>
       </c>
       <c r="C219" t="n">
-        <v>419.0187111847754</v>
+        <v>408.91239635591</v>
       </c>
       <c r="D219" t="n">
-        <v>407.1564763896412</v>
+        <v>397.8981811079678</v>
       </c>
       <c r="E219" t="n">
-        <v>417.1131700589296</v>
+        <v>405.5502747185776</v>
       </c>
       <c r="F219" t="n">
-        <v>13403200</v>
+        <v>11868600</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>46150</v>
+        <v>46160</v>
       </c>
       <c r="B220" t="n">
-        <v>410.7181396484375</v>
+        <v>395.0249328613281</v>
       </c>
       <c r="C220" t="n">
-        <v>416.025717257243</v>
+        <v>405.9293892063572</v>
       </c>
       <c r="D220" t="n">
-        <v>399.9433850490627</v>
+        <v>390.1363566382977</v>
       </c>
       <c r="E220" t="n">
-        <v>415.9758462562264</v>
+        <v>405.9293892063572</v>
       </c>
       <c r="F220" t="n">
-        <v>18531200</v>
+        <v>12117200</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>46153</v>
+        <v>46161</v>
       </c>
       <c r="B221" t="n">
-        <v>403.5948486328125</v>
+        <v>391.6926879882812</v>
       </c>
       <c r="C221" t="n">
-        <v>406.7773980105824</v>
+        <v>397.9480581917038</v>
       </c>
       <c r="D221" t="n">
-        <v>397.2596785679677</v>
+        <v>384.1603400520499</v>
       </c>
       <c r="E221" t="n">
-        <v>405.7896903250927</v>
+        <v>388.5999552120973</v>
       </c>
       <c r="F221" t="n">
-        <v>14680000</v>
+        <v>14083000</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>46154</v>
+        <v>46162</v>
       </c>
       <c r="B222" t="n">
-        <v>396.351806640625</v>
+        <v>400.6816711425781</v>
       </c>
       <c r="C222" t="n">
-        <v>401.3002097321041</v>
+        <v>402.9364007394573</v>
       </c>
       <c r="D222" t="n">
-        <v>385.2178768500887</v>
+        <v>395.0249352842741</v>
       </c>
       <c r="E222" t="n">
-        <v>396.8207097656788</v>
+        <v>396.0724699406183</v>
       </c>
       <c r="F222" t="n">
-        <v>18121800</v>
+        <v>10254300</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>46155</v>
+        <v>46163</v>
       </c>
       <c r="B223" t="n">
-        <v>398.8659057617188</v>
+        <v>406.19873046875</v>
       </c>
       <c r="C223" t="n">
-        <v>403.734509131243</v>
+        <v>410.4986581682928</v>
       </c>
       <c r="D223" t="n">
-        <v>390.5553811479706</v>
+        <v>398.5765963626999</v>
       </c>
       <c r="E223" t="n">
-        <v>397.3394816307741</v>
+        <v>398.5765963626999</v>
       </c>
       <c r="F223" t="n">
-        <v>13127800</v>
+        <v>8937900</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>46156</v>
+        <v>46164</v>
       </c>
       <c r="B224" t="n">
-        <v>416.7440490722656</v>
+        <v>403.5748901367188</v>
       </c>
       <c r="C224" t="n">
-        <v>420.9841194624343</v>
+        <v>409.7105459625166</v>
       </c>
       <c r="D224" t="n">
-        <v>401.1605481802736</v>
+        <v>401.9187648184228</v>
       </c>
       <c r="E224" t="n">
-        <v>402.2679401856103</v>
+        <v>408.4734223287576</v>
       </c>
       <c r="F224" t="n">
-        <v>18577100</v>
+        <v>7111900</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>46157</v>
+        <v>46168</v>
       </c>
       <c r="B225" t="n">
-        <v>403.4053039550781</v>
+        <v>411.3566589355469</v>
       </c>
       <c r="C225" t="n">
-        <v>408.91239635591</v>
+        <v>415.5168990579511</v>
       </c>
       <c r="D225" t="n">
-        <v>397.8981811079678</v>
+        <v>409.1119158569575</v>
       </c>
       <c r="E225" t="n">
-        <v>405.5502747185776</v>
+        <v>412.1547776294236</v>
       </c>
       <c r="F225" t="n">
-        <v>11868600</v>
+        <v>10132000</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>46160</v>
+        <v>46169</v>
       </c>
       <c r="B226" t="n">
-        <v>395.0249328613281</v>
+        <v>421.7423400878906</v>
       </c>
       <c r="C226" t="n">
-        <v>405.9293892063572</v>
+        <v>429.5440462174616</v>
       </c>
       <c r="D226" t="n">
-        <v>390.1363566382977</v>
+        <v>414.4095066168901</v>
       </c>
       <c r="E226" t="n">
-        <v>405.9293892063572</v>
+        <v>426.0222949648963</v>
       </c>
       <c r="F226" t="n">
-        <v>12117200</v>
+        <v>14695600</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>46161</v>
+        <v>46170</v>
       </c>
       <c r="B227" t="n">
-        <v>391.6926879882812</v>
+        <v>423.8673400878906</v>
       </c>
       <c r="C227" t="n">
-        <v>397.9480581917038</v>
+        <v>426.6009590399201</v>
       </c>
       <c r="D227" t="n">
-        <v>384.1603400520499</v>
+        <v>413.7410606943367</v>
       </c>
       <c r="E227" t="n">
-        <v>388.5999552120973</v>
+        <v>421.2335240308298</v>
       </c>
       <c r="F227" t="n">
-        <v>14083000</v>
+        <v>8905800</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>46162</v>
+        <v>46171</v>
       </c>
       <c r="B228" t="n">
-        <v>400.6816711425781</v>
+        <v>417.4723510742188</v>
       </c>
       <c r="C228" t="n">
-        <v>402.9364007394573</v>
+        <v>429.4343280523075</v>
       </c>
       <c r="D228" t="n">
-        <v>395.0249352842741</v>
+        <v>416.275142560005</v>
       </c>
       <c r="E228" t="n">
-        <v>396.0724699406183</v>
+        <v>426.0722065476131</v>
       </c>
       <c r="F228" t="n">
-        <v>10254300</v>
+        <v>11232300</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>46163</v>
+        <v>46174</v>
       </c>
       <c r="B229" t="n">
-        <v>406.19873046875</v>
+        <v>434.6122131347656</v>
       </c>
       <c r="C229" t="n">
-        <v>410.4986581682928</v>
+        <v>448.3400744619555</v>
       </c>
       <c r="D229" t="n">
-        <v>398.5765963626999</v>
+        <v>421.5128847675093</v>
       </c>
       <c r="E229" t="n">
-        <v>398.5765963626999</v>
+        <v>423.887329084468</v>
       </c>
       <c r="F229" t="n">
-        <v>8937900</v>
+        <v>18040400</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>46164</v>
+        <v>46175</v>
       </c>
       <c r="B230" t="n">
-        <v>403.5748901367188</v>
+        <v>445.6463623046875</v>
       </c>
       <c r="C230" t="n">
-        <v>409.7105459625166</v>
+        <v>447.3324162485465</v>
       </c>
       <c r="D230" t="n">
-        <v>401.9187648184228</v>
+        <v>434.9913222111342</v>
       </c>
       <c r="E230" t="n">
-        <v>408.4734223287576</v>
+        <v>439.550621789287</v>
       </c>
       <c r="F230" t="n">
-        <v>7111900</v>
+        <v>10147900</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>46168</v>
+        <v>46176</v>
       </c>
       <c r="B231" t="n">
-        <v>411.3566589355469</v>
+        <v>435.6697387695312</v>
       </c>
       <c r="C231" t="n">
-        <v>415.5168990579511</v>
+        <v>449.1082692608182</v>
       </c>
       <c r="D231" t="n">
-        <v>409.1119158569575</v>
+        <v>433.514781646741</v>
       </c>
       <c r="E231" t="n">
-        <v>412.1547776294236</v>
+        <v>448.9386530451177</v>
       </c>
       <c r="F231" t="n">
-        <v>10132000</v>
+        <v>10245200</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>46169</v>
+        <v>46177</v>
       </c>
       <c r="B232" t="n">
-        <v>421.7423400878906</v>
+        <v>443.8805236816406</v>
       </c>
       <c r="C232" t="n">
-        <v>429.5440462174616</v>
+        <v>446.9633007005261</v>
       </c>
       <c r="D232" t="n">
-        <v>414.4095066168901</v>
+        <v>426.3016646283289</v>
       </c>
       <c r="E232" t="n">
-        <v>426.0222949648963</v>
+        <v>429.6239016262129</v>
       </c>
       <c r="F232" t="n">
-        <v>14695600</v>
+        <v>10974100</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>46170</v>
+        <v>46178</v>
       </c>
       <c r="B233" t="n">
-        <v>423.8673400878906</v>
+        <v>414.2000122070312</v>
       </c>
       <c r="C233" t="n">
-        <v>426.6009590399201</v>
+        <v>432.8862320395821</v>
       </c>
       <c r="D233" t="n">
-        <v>413.7410606943367</v>
+        <v>411.8255679561694</v>
       </c>
       <c r="E233" t="n">
-        <v>421.2335240308298</v>
+        <v>428.7658764802955</v>
       </c>
       <c r="F233" t="n">
-        <v>8905800</v>
+        <v>19644200</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>46171</v>
+        <v>46181</v>
       </c>
       <c r="B234" t="n">
-        <v>417.4723510742188</v>
+        <v>425.8028259277344</v>
       </c>
       <c r="C234" t="n">
-        <v>429.4343280523075</v>
+        <v>432.7964577303483</v>
       </c>
       <c r="D234" t="n">
-        <v>416.275142560005</v>
+        <v>421.5428131800681</v>
       </c>
       <c r="E234" t="n">
-        <v>426.0722065476131</v>
+        <v>422.7799063408481</v>
       </c>
       <c r="F234" t="n">
-        <v>11232300</v>
+        <v>11245400</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>46174</v>
+        <v>46182</v>
       </c>
       <c r="B235" t="n">
-        <v>434.6122131347656</v>
+        <v>426.9202270507812</v>
       </c>
       <c r="C235" t="n">
-        <v>448.3400744619555</v>
+        <v>437.1362927141728</v>
       </c>
       <c r="D235" t="n">
-        <v>421.5128847675093</v>
+        <v>404.5625818100258</v>
       </c>
       <c r="E235" t="n">
-        <v>423.887329084468</v>
+        <v>429.8733028229284</v>
       </c>
       <c r="F235" t="n">
-        <v>18040400</v>
+        <v>21199500</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>46175</v>
+        <v>46183</v>
       </c>
       <c r="B236" t="n">
-        <v>445.6463623046875</v>
+        <v>407.7950134277344</v>
       </c>
       <c r="C236" t="n">
-        <v>447.3324162485465</v>
+        <v>425.3239709144749</v>
       </c>
       <c r="D236" t="n">
-        <v>434.9913222111342</v>
+        <v>406.7474787827616</v>
       </c>
       <c r="E236" t="n">
-        <v>439.550621789287</v>
+        <v>412.9928324745404</v>
       </c>
       <c r="F236" t="n">
-        <v>10147900</v>
+        <v>13139700</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>46176</v>
+        <v>46184</v>
       </c>
       <c r="B237" t="n">
-        <v>435.6697387695312</v>
+        <v>421.0700073242188</v>
       </c>
       <c r="C237" t="n">
-        <v>449.1082692608182</v>
+        <v>422.25</v>
       </c>
       <c r="D237" t="n">
-        <v>433.514781646741</v>
+        <v>408.8599853515625</v>
       </c>
       <c r="E237" t="n">
-        <v>448.9386530451177</v>
+        <v>413.260009765625</v>
       </c>
       <c r="F237" t="n">
-        <v>10245200</v>
+        <v>13826500</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>46177</v>
+        <v>46185</v>
       </c>
       <c r="B238" t="n">
-        <v>443.8805236816406</v>
+        <v>423.9299926757812</v>
       </c>
       <c r="C238" t="n">
-        <v>446.9633007005261</v>
+        <v>426.9400024414062</v>
       </c>
       <c r="D238" t="n">
-        <v>426.3016646283289</v>
+        <v>417.2099914550781</v>
       </c>
       <c r="E238" t="n">
-        <v>429.6239016262129</v>
+        <v>420.0499877929688</v>
       </c>
       <c r="F238" t="n">
-        <v>10974100</v>
+        <v>10362500</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>46178</v>
+        <v>46188</v>
       </c>
       <c r="B239" t="n">
-        <v>414.2000122070312</v>
+        <v>441.3999938964844</v>
       </c>
       <c r="C239" t="n">
-        <v>432.8862320395821</v>
+        <v>442.5799865722656</v>
       </c>
       <c r="D239" t="n">
-        <v>411.8255679561694</v>
+        <v>431.9299926757812</v>
       </c>
       <c r="E239" t="n">
-        <v>428.7658764802955</v>
+        <v>438.6799926757812</v>
       </c>
       <c r="F239" t="n">
-        <v>19644200</v>
+        <v>11184900</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>46181</v>
+        <v>46189</v>
       </c>
       <c r="B240" t="n">
-        <v>425.8028259277344</v>
+        <v>425.8299865722656</v>
       </c>
       <c r="C240" t="n">
-        <v>432.7964577303483</v>
+        <v>440.3299865722656</v>
       </c>
       <c r="D240" t="n">
-        <v>421.5428131800681</v>
+        <v>425.2000122070312</v>
       </c>
       <c r="E240" t="n">
-        <v>422.7799063408481</v>
+        <v>436.0199890136719</v>
       </c>
       <c r="F240" t="n">
-        <v>11245400</v>
+        <v>10943500</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>46182</v>
+        <v>46190</v>
       </c>
       <c r="B241" t="n">
-        <v>426.9202270507812</v>
+        <v>432.1499938964844</v>
       </c>
       <c r="C241" t="n">
-        <v>437.1362927141728</v>
+        <v>442.5</v>
       </c>
       <c r="D241" t="n">
-        <v>404.5625818100258</v>
+        <v>431.6400146484375</v>
       </c>
       <c r="E241" t="n">
-        <v>429.8733028229284</v>
+        <v>434.75</v>
       </c>
       <c r="F241" t="n">
-        <v>21199500</v>
+        <v>10934100</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>46183</v>
+        <v>46191</v>
       </c>
       <c r="B242" t="n">
-        <v>407.7950134277344</v>
+        <v>462.1199951171875</v>
       </c>
       <c r="C242" t="n">
-        <v>425.3239709144749</v>
+        <v>465.2200012207031</v>
       </c>
       <c r="D242" t="n">
-        <v>406.7474787827616</v>
+        <v>438.3900146484375</v>
       </c>
       <c r="E242" t="n">
-        <v>412.9928324745404</v>
+        <v>438.8800048828125</v>
       </c>
       <c r="F242" t="n">
-        <v>13139700</v>
+        <v>25817100</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
-        <v>46184</v>
+        <v>46195</v>
       </c>
       <c r="B243" t="n">
-        <v>421.0700073242188</v>
+        <v>467.6700134277344</v>
       </c>
       <c r="C243" t="n">
-        <v>422.25</v>
+        <v>476.7900085449219</v>
       </c>
       <c r="D243" t="n">
-        <v>408.8599853515625</v>
+        <v>465.1700134277344</v>
       </c>
       <c r="E243" t="n">
-        <v>413.260009765625</v>
+        <v>476.0899963378906</v>
       </c>
       <c r="F243" t="n">
-        <v>13826500</v>
+        <v>13686200</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
-        <v>46185</v>
+        <v>46196</v>
       </c>
       <c r="B244" t="n">
-        <v>423.9299926757812</v>
+        <v>436.3900146484375</v>
       </c>
       <c r="C244" t="n">
-        <v>426.9400024414062</v>
+        <v>447.3299865722656</v>
       </c>
       <c r="D244" t="n">
-        <v>417.2099914550781</v>
+        <v>434.1900024414062</v>
       </c>
       <c r="E244" t="n">
-        <v>420.0499877929688</v>
+        <v>439.1799926757812</v>
       </c>
       <c r="F244" t="n">
-        <v>10362500</v>
+        <v>20364500</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
-        <v>46188</v>
+        <v>46197</v>
       </c>
       <c r="B245" t="n">
-        <v>441.3999938964844</v>
+        <v>440.8299865722656</v>
       </c>
       <c r="C245" t="n">
-        <v>442.5799865722656</v>
+        <v>443.8599853515625</v>
       </c>
       <c r="D245" t="n">
-        <v>431.9299926757812</v>
+        <v>432.5799865722656</v>
       </c>
       <c r="E245" t="n">
-        <v>438.6799926757812</v>
+        <v>433.9800109863281</v>
       </c>
       <c r="F245" t="n">
-        <v>11184900</v>
+        <v>9991200</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
-        <v>46189</v>
+        <v>46198</v>
       </c>
       <c r="B246" t="n">
-        <v>425.8299865722656</v>
+        <v>434.989990234375</v>
       </c>
       <c r="C246" t="n">
-        <v>440.3299865722656</v>
+        <v>452.8999938964844</v>
       </c>
       <c r="D246" t="n">
-        <v>425.2000122070312</v>
+        <v>432.4400024414062</v>
       </c>
       <c r="E246" t="n">
-        <v>436.0199890136719</v>
+        <v>452.8999938964844</v>
       </c>
       <c r="F246" t="n">
-        <v>10943500</v>
+        <v>14769500</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
-        <v>46190</v>
+        <v>46199</v>
       </c>
       <c r="B247" t="n">
-        <v>432.1499938964844</v>
+        <v>432.3500061035156</v>
       </c>
       <c r="C247" t="n">
-        <v>442.5</v>
+        <v>436.1300048828125</v>
       </c>
       <c r="D247" t="n">
-        <v>431.6400146484375</v>
+        <v>419.1900024414062</v>
       </c>
       <c r="E247" t="n">
-        <v>434.75</v>
+        <v>425</v>
       </c>
       <c r="F247" t="n">
-        <v>10934100</v>
+        <v>17974100</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
-        <v>46191</v>
+        <v>46202</v>
       </c>
       <c r="B248" t="n">
-        <v>462.1199951171875</v>
+        <v>455.1000061035156</v>
       </c>
       <c r="C248" t="n">
-        <v>465.2200012207031</v>
+        <v>456.1000061035156</v>
       </c>
       <c r="D248" t="n">
-        <v>438.3900146484375</v>
+        <v>431.0899963378906</v>
       </c>
       <c r="E248" t="n">
-        <v>438.8800048828125</v>
+        <v>437</v>
       </c>
       <c r="F248" t="n">
-        <v>25817100</v>
+        <v>14881400</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
-        <v>46195</v>
+        <v>46203</v>
       </c>
       <c r="B249" t="n">
-        <v>467.6700134277344</v>
+        <v>477.5700073242188</v>
       </c>
       <c r="C249" t="n">
-        <v>476.7900085449219</v>
+        <v>479</v>
       </c>
       <c r="D249" t="n">
-        <v>465.1700134277344</v>
+        <v>453</v>
       </c>
       <c r="E249" t="n">
-        <v>476.0899963378906</v>
+        <v>455.6099853515625</v>
       </c>
       <c r="F249" t="n">
-        <v>13686200</v>
+        <v>15074300</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
-        <v>46196</v>
+        <v>46204</v>
       </c>
       <c r="B250" t="n">
-        <v>436.3900146484375</v>
+        <v>444.2300109863281</v>
       </c>
       <c r="C250" t="n">
-        <v>447.3299865722656</v>
+        <v>468.510009765625</v>
       </c>
       <c r="D250" t="n">
-        <v>434.1900024414062</v>
+        <v>443.4700012207031</v>
       </c>
       <c r="E250" t="n">
-        <v>439.1799926757812</v>
+        <v>467.6700134277344</v>
       </c>
       <c r="F250" t="n">
-        <v>20364500</v>
+        <v>18534800</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>46197</v>
+        <v>46205</v>
       </c>
       <c r="B251" t="n">
-        <v>440.8299865722656</v>
+        <v>434.1600036621094</v>
       </c>
       <c r="C251" t="n">
-        <v>443.8599853515625</v>
+        <v>461.4700012207031</v>
       </c>
       <c r="D251" t="n">
-        <v>432.5799865722656</v>
+        <v>429.5</v>
       </c>
       <c r="E251" t="n">
-        <v>433.9800109863281</v>
+        <v>450.5400085449219</v>
       </c>
       <c r="F251" t="n">
-        <v>9991200</v>
+        <v>18375000</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="n">
-        <v>46198</v>
+        <v>46209</v>
       </c>
       <c r="B252" t="n">
-        <v>434.989990234375</v>
+        <v>451.7900085449219</v>
       </c>
       <c r="C252" t="n">
-        <v>452.55810546875</v>
+        <v>460.0249938964844</v>
       </c>
       <c r="D252" t="n">
-        <v>432.5</v>
+        <v>445.6000061035156</v>
       </c>
       <c r="E252" t="n">
-        <v>452.8999938964844</v>
+        <v>447.7749938964844</v>
       </c>
       <c r="F252" t="n">
-        <v>12662198</v>
+        <v>12429831</v>
       </c>
     </row>
   </sheetData>
